--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>NIO</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,29 +717,32 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>6803000</v>
+        <v>7732000</v>
       </c>
       <c r="E8" s="3">
-        <v>4989700</v>
+        <v>6849300</v>
       </c>
       <c r="F8" s="3">
-        <v>2244900</v>
+        <v>5023700</v>
       </c>
       <c r="G8" s="3">
-        <v>1080500</v>
+        <v>2260200</v>
       </c>
       <c r="H8" s="3">
-        <v>683700</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
+        <v>1087800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>688300</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -756,32 +759,35 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6092700</v>
+        <v>7307700</v>
       </c>
       <c r="E9" s="3">
-        <v>4047800</v>
+        <v>6134200</v>
       </c>
       <c r="F9" s="3">
-        <v>1986200</v>
+        <v>4075400</v>
       </c>
       <c r="G9" s="3">
-        <v>1246000</v>
+        <v>1999700</v>
       </c>
       <c r="H9" s="3">
-        <v>719000</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+        <v>1254500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>723900</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -801,29 +807,32 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>710300</v>
+        <v>424300</v>
       </c>
       <c r="E10" s="3">
-        <v>941900</v>
+        <v>715100</v>
       </c>
       <c r="F10" s="3">
-        <v>258700</v>
+        <v>948300</v>
       </c>
       <c r="G10" s="3">
-        <v>-165500</v>
+        <v>260400</v>
       </c>
       <c r="H10" s="3">
-        <v>-35300</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+        <v>-166700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-35600</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,35 +874,36 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1450300</v>
+        <v>1867200</v>
       </c>
       <c r="E12" s="3">
-        <v>604500</v>
+        <v>1460100</v>
       </c>
       <c r="F12" s="3">
-        <v>308200</v>
+        <v>608600</v>
       </c>
       <c r="G12" s="3">
-        <v>585700</v>
+        <v>310300</v>
       </c>
       <c r="H12" s="3">
-        <v>537800</v>
+        <v>589600</v>
       </c>
       <c r="I12" s="3">
-        <v>354000</v>
+        <v>541400</v>
       </c>
       <c r="J12" s="3">
+        <v>356400</v>
+      </c>
+      <c r="K12" s="3">
         <v>201300</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,17 +961,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>-23700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-19200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -972,8 +991,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -987,36 +1006,39 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>112900</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>76200</v>
+        <v>113600</v>
       </c>
       <c r="F15" s="3">
-        <v>80200</v>
+        <v>76700</v>
       </c>
       <c r="G15" s="3">
-        <v>89000</v>
+        <v>80800</v>
       </c>
       <c r="H15" s="3">
-        <v>48800</v>
+        <v>89600</v>
       </c>
       <c r="I15" s="3">
-        <v>23200</v>
+        <v>49100</v>
       </c>
       <c r="J15" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K15" s="3">
         <v>6400</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,35 +1070,36 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8943600</v>
+        <v>10857900</v>
       </c>
       <c r="E17" s="3">
-        <v>5610600</v>
+        <v>9004400</v>
       </c>
       <c r="F17" s="3">
-        <v>2881100</v>
+        <v>5648800</v>
       </c>
       <c r="G17" s="3">
-        <v>2610300</v>
+        <v>2900700</v>
       </c>
       <c r="H17" s="3">
-        <v>2008600</v>
+        <v>2628000</v>
       </c>
       <c r="I17" s="3">
-        <v>684000</v>
+        <v>2022300</v>
       </c>
       <c r="J17" s="3">
+        <v>688600</v>
+      </c>
+      <c r="K17" s="3">
         <v>359400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,29 +1112,32 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2140600</v>
+        <v>-3125900</v>
       </c>
       <c r="E18" s="3">
-        <v>-620800</v>
+        <v>-2155100</v>
       </c>
       <c r="F18" s="3">
-        <v>-636200</v>
+        <v>-625100</v>
       </c>
       <c r="G18" s="3">
-        <v>-1529800</v>
+        <v>-640600</v>
       </c>
       <c r="H18" s="3">
-        <v>-1325000</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+        <v>-1540200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1334000</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,28 +1179,29 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200700</v>
+        <v>337800</v>
       </c>
       <c r="E20" s="3">
-        <v>160000</v>
+        <v>202100</v>
       </c>
       <c r="F20" s="3">
-        <v>-36500</v>
+        <v>161100</v>
       </c>
       <c r="G20" s="3">
-        <v>22400</v>
+        <v>-36700</v>
       </c>
       <c r="H20" s="3">
-        <v>14100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+        <v>22500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>14200</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1188,29 +1221,32 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-1546200</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>-225100</v>
+        <v>-1556100</v>
       </c>
       <c r="F21" s="3">
-        <v>-528300</v>
+        <v>-226300</v>
       </c>
       <c r="G21" s="3">
-        <v>-1369600</v>
+        <v>-531600</v>
       </c>
       <c r="H21" s="3">
-        <v>-1245400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>-1378700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1253800</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1230,35 +1266,38 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>46000</v>
+        <v>56100</v>
       </c>
       <c r="E22" s="3">
-        <v>88000</v>
+        <v>46300</v>
       </c>
       <c r="F22" s="3">
-        <v>58800</v>
+        <v>88600</v>
       </c>
       <c r="G22" s="3">
-        <v>51200</v>
+        <v>59200</v>
       </c>
       <c r="H22" s="3">
-        <v>17100</v>
+        <v>51500</v>
       </c>
       <c r="I22" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J22" s="3">
         <v>2500</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1272,36 +1311,39 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1985900</v>
+        <v>-2844200</v>
       </c>
       <c r="E23" s="3">
-        <v>-548800</v>
+        <v>-1999400</v>
       </c>
       <c r="F23" s="3">
-        <v>-731500</v>
+        <v>-552600</v>
       </c>
       <c r="G23" s="3">
-        <v>-1558600</v>
+        <v>-736500</v>
       </c>
       <c r="H23" s="3">
-        <v>-1327900</v>
+        <v>-1569200</v>
       </c>
       <c r="I23" s="3">
-        <v>-692200</v>
+        <v>-1336900</v>
       </c>
       <c r="J23" s="3">
+        <v>-696900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-354700</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,36 +1356,39 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7600</v>
+        <v>36300</v>
       </c>
       <c r="E24" s="3">
-        <v>5800</v>
+        <v>7700</v>
       </c>
       <c r="F24" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
-        <v>3000</v>
-      </c>
       <c r="I24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,36 +1446,39 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1993500</v>
+        <v>-2880500</v>
       </c>
       <c r="E26" s="3">
-        <v>-554700</v>
+        <v>-2007000</v>
       </c>
       <c r="F26" s="3">
-        <v>-732400</v>
+        <v>-558400</v>
       </c>
       <c r="G26" s="3">
-        <v>-1559700</v>
+        <v>-737400</v>
       </c>
       <c r="H26" s="3">
-        <v>-1331000</v>
+        <v>-1570300</v>
       </c>
       <c r="I26" s="3">
-        <v>-693300</v>
+        <v>-1340000</v>
       </c>
       <c r="J26" s="3">
+        <v>-698000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-355300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,36 +1491,39 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2010400</v>
+        <v>-2939900</v>
       </c>
       <c r="E27" s="3">
-        <v>-1459800</v>
+        <v>-2024100</v>
       </c>
       <c r="F27" s="3">
-        <v>-774700</v>
+        <v>-1469800</v>
       </c>
       <c r="G27" s="3">
-        <v>-1575900</v>
+        <v>-780000</v>
       </c>
       <c r="H27" s="3">
-        <v>-3221100</v>
+        <v>-1586600</v>
       </c>
       <c r="I27" s="3">
-        <v>-1044100</v>
+        <v>-3243000</v>
       </c>
       <c r="J27" s="3">
+        <v>-1051200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-485700</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,29 +1716,32 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200700</v>
+        <v>-337800</v>
       </c>
       <c r="E32" s="3">
-        <v>-160000</v>
+        <v>-202100</v>
       </c>
       <c r="F32" s="3">
-        <v>36500</v>
+        <v>-161100</v>
       </c>
       <c r="G32" s="3">
-        <v>-22400</v>
+        <v>36700</v>
       </c>
       <c r="H32" s="3">
-        <v>-14100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+        <v>-22500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-14200</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1692,36 +1761,39 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2010400</v>
+        <v>-2939900</v>
       </c>
       <c r="E33" s="3">
-        <v>-1459800</v>
+        <v>-2024100</v>
       </c>
       <c r="F33" s="3">
-        <v>-774700</v>
+        <v>-1469800</v>
       </c>
       <c r="G33" s="3">
-        <v>-1575900</v>
+        <v>-780000</v>
       </c>
       <c r="H33" s="3">
-        <v>-3221100</v>
+        <v>-1586600</v>
       </c>
       <c r="I33" s="3">
-        <v>-1044100</v>
+        <v>-3243000</v>
       </c>
       <c r="J33" s="3">
+        <v>-1051200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-485700</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,36 +1851,39 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2010400</v>
+        <v>-2939900</v>
       </c>
       <c r="E35" s="3">
-        <v>-1459800</v>
+        <v>-2024100</v>
       </c>
       <c r="F35" s="3">
-        <v>-774700</v>
+        <v>-1469800</v>
       </c>
       <c r="G35" s="3">
-        <v>-1575900</v>
+        <v>-780000</v>
       </c>
       <c r="H35" s="3">
-        <v>-3221100</v>
+        <v>-1586600</v>
       </c>
       <c r="I35" s="3">
-        <v>-1044100</v>
+        <v>-3243000</v>
       </c>
       <c r="J35" s="3">
+        <v>-1051200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-485700</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,41 +1896,44 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,35 +1987,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2746100</v>
+        <v>4578600</v>
       </c>
       <c r="E41" s="3">
-        <v>2117300</v>
+        <v>2764800</v>
       </c>
       <c r="F41" s="3">
-        <v>5305800</v>
+        <v>2131700</v>
       </c>
       <c r="G41" s="3">
-        <v>119100</v>
+        <v>5341900</v>
       </c>
       <c r="H41" s="3">
-        <v>432700</v>
+        <v>120000</v>
       </c>
       <c r="I41" s="3">
-        <v>1036400</v>
+        <v>435700</v>
       </c>
       <c r="J41" s="3">
+        <v>1043500</v>
+      </c>
+      <c r="K41" s="3">
         <v>80300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,29 +2029,32 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2647100</v>
+        <v>2336900</v>
       </c>
       <c r="E42" s="3">
-        <v>5116900</v>
+        <v>2665200</v>
       </c>
       <c r="F42" s="3">
-        <v>545500</v>
+        <v>5151700</v>
       </c>
       <c r="G42" s="3">
-        <v>15300</v>
+        <v>549200</v>
       </c>
       <c r="H42" s="3">
-        <v>711800</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+        <v>15400</v>
+      </c>
+      <c r="I42" s="3">
+        <v>716600</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -1982,39 +2071,42 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1023300</v>
+        <v>887000</v>
       </c>
       <c r="E43" s="3">
-        <v>774800</v>
+        <v>1030200</v>
       </c>
       <c r="F43" s="3">
-        <v>330800</v>
+        <v>780100</v>
       </c>
       <c r="G43" s="3">
-        <v>389400</v>
+        <v>333100</v>
       </c>
       <c r="H43" s="3">
-        <v>276500</v>
+        <v>392000</v>
       </c>
       <c r="I43" s="3">
-        <v>69900</v>
+        <v>278300</v>
       </c>
       <c r="J43" s="3">
+        <v>70300</v>
+      </c>
+      <c r="K43" s="3">
         <v>25300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,35 +2119,38 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1131100</v>
+        <v>733700</v>
       </c>
       <c r="E44" s="3">
-        <v>283900</v>
+        <v>1138800</v>
       </c>
       <c r="F44" s="3">
-        <v>149300</v>
+        <v>285900</v>
       </c>
       <c r="G44" s="3">
-        <v>122800</v>
+        <v>150400</v>
       </c>
       <c r="H44" s="3">
-        <v>202300</v>
+        <v>123700</v>
       </c>
       <c r="I44" s="3">
+        <v>203700</v>
+      </c>
+      <c r="J44" s="3">
         <v>12400</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -2069,36 +2164,39 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>619800</v>
+        <v>1248000</v>
       </c>
       <c r="E45" s="3">
-        <v>494600</v>
+        <v>624100</v>
       </c>
       <c r="F45" s="3">
-        <v>48800</v>
+        <v>498000</v>
       </c>
       <c r="G45" s="3">
-        <v>33800</v>
+        <v>49100</v>
       </c>
       <c r="H45" s="3">
-        <v>57100</v>
+        <v>34000</v>
       </c>
       <c r="I45" s="3">
-        <v>28800</v>
+        <v>57500</v>
       </c>
       <c r="J45" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K45" s="3">
         <v>15300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,36 +2209,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8167400</v>
+        <v>9784300</v>
       </c>
       <c r="E46" s="3">
-        <v>8787600</v>
+        <v>8223000</v>
       </c>
       <c r="F46" s="3">
-        <v>6380200</v>
+        <v>8847400</v>
       </c>
       <c r="G46" s="3">
-        <v>680500</v>
+        <v>6423700</v>
       </c>
       <c r="H46" s="3">
-        <v>1680400</v>
+        <v>685100</v>
       </c>
       <c r="I46" s="3">
-        <v>1147400</v>
+        <v>1691800</v>
       </c>
       <c r="J46" s="3">
+        <v>1155300</v>
+      </c>
+      <c r="K46" s="3">
         <v>120800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,35 +2254,38 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1699200</v>
+        <v>762800</v>
       </c>
       <c r="E47" s="3">
-        <v>1044600</v>
+        <v>1710800</v>
       </c>
       <c r="F47" s="3">
-        <v>219400</v>
+        <v>1051700</v>
       </c>
       <c r="G47" s="3">
-        <v>106700</v>
+        <v>220900</v>
       </c>
       <c r="H47" s="3">
-        <v>100900</v>
+        <v>107500</v>
       </c>
       <c r="I47" s="3">
-        <v>13400</v>
+        <v>101600</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
+        <v>13500</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
@@ -2195,36 +2299,39 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3187200</v>
+        <v>5039600</v>
       </c>
       <c r="E48" s="3">
-        <v>1443500</v>
+        <v>3208900</v>
       </c>
       <c r="F48" s="3">
-        <v>889600</v>
+        <v>1453300</v>
       </c>
       <c r="G48" s="3">
-        <v>1061300</v>
+        <v>895600</v>
       </c>
       <c r="H48" s="3">
-        <v>670100</v>
+        <v>1068500</v>
       </c>
       <c r="I48" s="3">
-        <v>263900</v>
+        <v>674700</v>
       </c>
       <c r="J48" s="3">
+        <v>265700</v>
+      </c>
+      <c r="K48" s="3">
         <v>115000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,36 +2344,39 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>29400</v>
+        <v>32900</v>
       </c>
       <c r="E49" s="3">
-        <v>27500</v>
+        <v>29600</v>
       </c>
       <c r="F49" s="3">
-        <v>28200</v>
+        <v>27700</v>
       </c>
       <c r="G49" s="3">
-        <v>29000</v>
+        <v>28400</v>
       </c>
       <c r="H49" s="3">
-        <v>30000</v>
+        <v>29200</v>
       </c>
       <c r="I49" s="3">
+        <v>30200</v>
+      </c>
+      <c r="J49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,36 +2479,39 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>209000</v>
+        <v>698900</v>
       </c>
       <c r="E52" s="3">
-        <v>141400</v>
+        <v>210400</v>
       </c>
       <c r="F52" s="3">
-        <v>27500</v>
+        <v>142400</v>
       </c>
       <c r="G52" s="3">
-        <v>136000</v>
+        <v>27700</v>
       </c>
       <c r="H52" s="3">
-        <v>120400</v>
+        <v>136900</v>
       </c>
       <c r="I52" s="3">
-        <v>20100</v>
+        <v>121200</v>
       </c>
       <c r="J52" s="3">
+        <v>20200</v>
+      </c>
+      <c r="K52" s="3">
         <v>7700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,36 +2569,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>13292100</v>
+        <v>16318600</v>
       </c>
       <c r="E54" s="3">
-        <v>11444600</v>
+        <v>13382600</v>
       </c>
       <c r="F54" s="3">
-        <v>7545000</v>
+        <v>11522500</v>
       </c>
       <c r="G54" s="3">
-        <v>2013500</v>
+        <v>7596300</v>
       </c>
       <c r="H54" s="3">
-        <v>2601800</v>
+        <v>2027200</v>
       </c>
       <c r="I54" s="3">
-        <v>1445400</v>
+        <v>2619500</v>
       </c>
       <c r="J54" s="3">
+        <v>1455300</v>
+      </c>
+      <c r="K54" s="3">
         <v>244500</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,35 +2655,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4059100</v>
+        <v>4138100</v>
       </c>
       <c r="E57" s="3">
-        <v>1946600</v>
+        <v>4086700</v>
       </c>
       <c r="F57" s="3">
-        <v>978100</v>
+        <v>1959900</v>
       </c>
       <c r="G57" s="3">
-        <v>584500</v>
+        <v>984800</v>
       </c>
       <c r="H57" s="3">
-        <v>538100</v>
+        <v>588500</v>
       </c>
       <c r="I57" s="3">
-        <v>89000</v>
+        <v>541800</v>
       </c>
       <c r="J57" s="3">
+        <v>89600</v>
+      </c>
+      <c r="K57" s="3">
         <v>26300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,36 +2697,39 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>732900</v>
+        <v>1365400</v>
       </c>
       <c r="E58" s="3">
-        <v>1011500</v>
+        <v>737900</v>
       </c>
       <c r="F58" s="3">
-        <v>271200</v>
+        <v>1018400</v>
       </c>
       <c r="G58" s="3">
-        <v>172400</v>
+        <v>273000</v>
       </c>
       <c r="H58" s="3">
-        <v>285700</v>
+        <v>173600</v>
       </c>
       <c r="I58" s="3">
-        <v>11600</v>
+        <v>287600</v>
       </c>
       <c r="J58" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,36 +2742,39 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1539300</v>
+        <v>2531600</v>
       </c>
       <c r="E59" s="3">
-        <v>1073500</v>
+        <v>1549800</v>
       </c>
       <c r="F59" s="3">
-        <v>680500</v>
+        <v>1080800</v>
       </c>
       <c r="G59" s="3">
-        <v>554700</v>
+        <v>685200</v>
       </c>
       <c r="H59" s="3">
-        <v>362800</v>
+        <v>558500</v>
       </c>
       <c r="I59" s="3">
-        <v>122900</v>
+        <v>365200</v>
       </c>
       <c r="J59" s="3">
+        <v>123700</v>
+      </c>
+      <c r="K59" s="3">
         <v>71300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,36 +2787,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6331300</v>
+        <v>8035100</v>
       </c>
       <c r="E60" s="3">
-        <v>4031700</v>
+        <v>6374400</v>
       </c>
       <c r="F60" s="3">
-        <v>1929800</v>
+        <v>4059100</v>
       </c>
       <c r="G60" s="3">
-        <v>1311600</v>
+        <v>1943000</v>
       </c>
       <c r="H60" s="3">
-        <v>1186600</v>
+        <v>1320500</v>
       </c>
       <c r="I60" s="3">
-        <v>223500</v>
+        <v>1194700</v>
       </c>
       <c r="J60" s="3">
+        <v>225000</v>
+      </c>
+      <c r="K60" s="3">
         <v>100300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,36 +2832,39 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1505100</v>
+        <v>1813200</v>
       </c>
       <c r="E61" s="3">
-        <v>1349200</v>
+        <v>1515400</v>
       </c>
       <c r="F61" s="3">
-        <v>827600</v>
+        <v>1358300</v>
       </c>
       <c r="G61" s="3">
-        <v>1000200</v>
+        <v>833200</v>
       </c>
       <c r="H61" s="3">
-        <v>161300</v>
+        <v>1007000</v>
       </c>
       <c r="I61" s="3">
-        <v>88700</v>
+        <v>162400</v>
       </c>
       <c r="J61" s="3">
+        <v>89300</v>
+      </c>
+      <c r="K61" s="3">
         <v>5200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,36 +2877,39 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1638300</v>
+        <v>2355900</v>
       </c>
       <c r="E62" s="3">
-        <v>807900</v>
+        <v>1649500</v>
       </c>
       <c r="F62" s="3">
-        <v>388000</v>
+        <v>813400</v>
       </c>
       <c r="G62" s="3">
-        <v>367500</v>
+        <v>390700</v>
       </c>
       <c r="H62" s="3">
-        <v>128500</v>
+        <v>370000</v>
       </c>
       <c r="I62" s="3">
-        <v>19500</v>
+        <v>129400</v>
       </c>
       <c r="J62" s="3">
+        <v>19600</v>
+      </c>
+      <c r="K62" s="3">
         <v>8500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,36 +3057,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9996400</v>
+        <v>12767200</v>
       </c>
       <c r="E66" s="3">
-        <v>6651800</v>
+        <v>10064500</v>
       </c>
       <c r="F66" s="3">
-        <v>3793500</v>
+        <v>6697100</v>
       </c>
       <c r="G66" s="3">
-        <v>2883300</v>
+        <v>3819300</v>
       </c>
       <c r="H66" s="3">
-        <v>1657700</v>
+        <v>2903000</v>
       </c>
       <c r="I66" s="3">
-        <v>333200</v>
+        <v>1669000</v>
       </c>
       <c r="J66" s="3">
+        <v>335500</v>
+      </c>
+      <c r="K66" s="3">
         <v>112400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3069,14 +3236,14 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>2714300</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>2732800</v>
+      </c>
+      <c r="K70" s="3">
         <v>671300</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,36 +3301,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-9653800</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E72" s="3">
-        <v>-7682000</v>
+        <v>-9719500</v>
       </c>
       <c r="F72" s="3">
-        <v>-7131600</v>
+        <v>-7734300</v>
       </c>
       <c r="G72" s="3">
-        <v>-6396700</v>
+        <v>-7180200</v>
       </c>
       <c r="H72" s="3">
-        <v>-4838300</v>
+        <v>-6440300</v>
       </c>
       <c r="I72" s="3">
-        <v>-1617200</v>
+        <v>-4871200</v>
       </c>
       <c r="J72" s="3">
+        <v>-1628200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-562900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,36 +3481,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3295700</v>
+        <v>3551400</v>
       </c>
       <c r="E76" s="3">
-        <v>4792700</v>
+        <v>3318200</v>
       </c>
       <c r="F76" s="3">
-        <v>3751500</v>
+        <v>4825400</v>
       </c>
       <c r="G76" s="3">
-        <v>-869900</v>
+        <v>3777000</v>
       </c>
       <c r="H76" s="3">
-        <v>944100</v>
+        <v>-875800</v>
       </c>
       <c r="I76" s="3">
-        <v>-1602100</v>
+        <v>950500</v>
       </c>
       <c r="J76" s="3">
+        <v>-1613000</v>
+      </c>
+      <c r="K76" s="3">
         <v>-539200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,41 +3571,44 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,36 +3621,39 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2010400</v>
+        <v>-2939900</v>
       </c>
       <c r="E81" s="3">
-        <v>-1459800</v>
+        <v>-2024100</v>
       </c>
       <c r="F81" s="3">
-        <v>-774700</v>
+        <v>-1469800</v>
       </c>
       <c r="G81" s="3">
-        <v>-1575900</v>
+        <v>-780000</v>
       </c>
       <c r="H81" s="3">
-        <v>-3221100</v>
+        <v>-1586600</v>
       </c>
       <c r="I81" s="3">
-        <v>-1044100</v>
+        <v>-3243000</v>
       </c>
       <c r="J81" s="3">
+        <v>-1051200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-485700</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>393800</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
-        <v>235800</v>
+        <v>396500</v>
       </c>
       <c r="F83" s="3">
-        <v>144500</v>
+        <v>237400</v>
       </c>
       <c r="G83" s="3">
-        <v>137900</v>
+        <v>145500</v>
       </c>
       <c r="H83" s="3">
-        <v>65500</v>
+        <v>138900</v>
       </c>
       <c r="I83" s="3">
-        <v>23200</v>
+        <v>65900</v>
       </c>
       <c r="J83" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K83" s="3">
         <v>6400</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,36 +3955,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-533800</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>271500</v>
+        <v>-537500</v>
       </c>
       <c r="F89" s="3">
-        <v>269400</v>
+        <v>273400</v>
       </c>
       <c r="G89" s="3">
-        <v>-1204300</v>
+        <v>271200</v>
       </c>
       <c r="H89" s="3">
-        <v>-1092500</v>
+        <v>-1212500</v>
       </c>
       <c r="I89" s="3">
-        <v>-631700</v>
+        <v>-1099900</v>
       </c>
       <c r="J89" s="3">
+        <v>-636000</v>
+      </c>
+      <c r="K89" s="3">
         <v>-304000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,35 +4022,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-962800</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-563200</v>
+        <v>-969400</v>
       </c>
       <c r="F91" s="3">
-        <v>-155700</v>
+        <v>-567000</v>
       </c>
       <c r="G91" s="3">
-        <v>-235700</v>
+        <v>-156800</v>
       </c>
       <c r="H91" s="3">
-        <v>-365100</v>
+        <v>-237300</v>
       </c>
       <c r="I91" s="3">
-        <v>-153800</v>
+        <v>-367600</v>
       </c>
       <c r="J91" s="3">
+        <v>-154900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-90400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,36 +4154,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>1434000</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>-5490700</v>
+        <v>1443700</v>
       </c>
       <c r="F94" s="3">
-        <v>-700200</v>
+        <v>-5528100</v>
       </c>
       <c r="G94" s="3">
-        <v>467000</v>
+        <v>-705000</v>
       </c>
       <c r="H94" s="3">
-        <v>-1096500</v>
+        <v>470200</v>
       </c>
       <c r="I94" s="3">
-        <v>-164400</v>
+        <v>-1103900</v>
       </c>
       <c r="J94" s="3">
+        <v>-165500</v>
+      </c>
+      <c r="K94" s="3">
         <v>16300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4398,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-223200</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
-        <v>2503200</v>
+        <v>-224700</v>
       </c>
       <c r="F100" s="3">
-        <v>5710600</v>
+        <v>2520300</v>
       </c>
       <c r="G100" s="3">
-        <v>427400</v>
+        <v>5749500</v>
       </c>
       <c r="H100" s="3">
-        <v>1602200</v>
+        <v>430300</v>
       </c>
       <c r="I100" s="3">
-        <v>1776700</v>
+        <v>1613100</v>
       </c>
       <c r="J100" s="3">
+        <v>1788800</v>
+      </c>
+      <c r="K100" s="3">
         <v>316600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,36 +4443,39 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-16800</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
-        <v>-69200</v>
+        <v>-16900</v>
       </c>
       <c r="F101" s="3">
-        <v>-94200</v>
+        <v>-69600</v>
       </c>
       <c r="G101" s="3">
+        <v>-94800</v>
+      </c>
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7900</v>
       </c>
-      <c r="I101" s="3">
-        <v>-23200</v>
-      </c>
       <c r="J101" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="K101" s="3">
         <v>5600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,36 +4488,39 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>660100</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E102" s="3">
-        <v>-2785100</v>
+        <v>664600</v>
       </c>
       <c r="F102" s="3">
-        <v>5185600</v>
+        <v>-2804100</v>
       </c>
       <c r="G102" s="3">
-        <v>-308500</v>
+        <v>5220900</v>
       </c>
       <c r="H102" s="3">
-        <v>-594600</v>
+        <v>-310600</v>
       </c>
       <c r="I102" s="3">
-        <v>957500</v>
+        <v>-598700</v>
       </c>
       <c r="J102" s="3">
+        <v>964000</v>
+      </c>
+      <c r="K102" s="3">
         <v>34500</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>NIO</t>
   </si>
@@ -662,7 +662,8 @@
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -727,22 +728,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>7732000</v>
+        <v>7684200</v>
       </c>
       <c r="E8" s="3">
-        <v>6849300</v>
+        <v>6806900</v>
       </c>
       <c r="F8" s="3">
-        <v>5023700</v>
+        <v>4992600</v>
       </c>
       <c r="G8" s="3">
-        <v>2260200</v>
+        <v>2246200</v>
       </c>
       <c r="H8" s="3">
-        <v>1087800</v>
+        <v>1081100</v>
       </c>
       <c r="I8" s="3">
-        <v>688300</v>
+        <v>684100</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -772,22 +773,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>7307700</v>
+        <v>7262500</v>
       </c>
       <c r="E9" s="3">
-        <v>6134200</v>
+        <v>6096300</v>
       </c>
       <c r="F9" s="3">
-        <v>4075400</v>
+        <v>4050200</v>
       </c>
       <c r="G9" s="3">
-        <v>1999700</v>
+        <v>1987400</v>
       </c>
       <c r="H9" s="3">
-        <v>1254500</v>
+        <v>1246700</v>
       </c>
       <c r="I9" s="3">
-        <v>723900</v>
+        <v>719400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -817,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>424300</v>
+        <v>421600</v>
       </c>
       <c r="E10" s="3">
-        <v>715100</v>
+        <v>710700</v>
       </c>
       <c r="F10" s="3">
-        <v>948300</v>
+        <v>942400</v>
       </c>
       <c r="G10" s="3">
-        <v>260400</v>
+        <v>258800</v>
       </c>
       <c r="H10" s="3">
-        <v>-166700</v>
+        <v>-165600</v>
       </c>
       <c r="I10" s="3">
-        <v>-35600</v>
+        <v>-35400</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -881,25 +882,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1867200</v>
+        <v>1756100</v>
       </c>
       <c r="E12" s="3">
-        <v>1460100</v>
+        <v>1451100</v>
       </c>
       <c r="F12" s="3">
-        <v>608600</v>
+        <v>604800</v>
       </c>
       <c r="G12" s="3">
-        <v>310300</v>
+        <v>308400</v>
       </c>
       <c r="H12" s="3">
-        <v>589600</v>
+        <v>586000</v>
       </c>
       <c r="I12" s="3">
-        <v>541400</v>
+        <v>538100</v>
       </c>
       <c r="J12" s="3">
-        <v>356400</v>
+        <v>354200</v>
       </c>
       <c r="K12" s="3">
         <v>201300</v>
@@ -971,10 +972,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-23700</v>
+        <v>-23500</v>
       </c>
       <c r="E14" s="3">
-        <v>-19200</v>
+        <v>-19100</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1015,26 +1016,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>192500</v>
       </c>
       <c r="E15" s="3">
-        <v>113600</v>
+        <v>112900</v>
       </c>
       <c r="F15" s="3">
-        <v>76700</v>
+        <v>76300</v>
       </c>
       <c r="G15" s="3">
-        <v>80800</v>
+        <v>80300</v>
       </c>
       <c r="H15" s="3">
-        <v>89600</v>
+        <v>89000</v>
       </c>
       <c r="I15" s="3">
-        <v>49100</v>
+        <v>48800</v>
       </c>
       <c r="J15" s="3">
-        <v>23300</v>
+        <v>23200</v>
       </c>
       <c r="K15" s="3">
         <v>6400</v>
@@ -1077,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10857900</v>
+        <v>10790700</v>
       </c>
       <c r="E17" s="3">
-        <v>9004400</v>
+        <v>8948700</v>
       </c>
       <c r="F17" s="3">
-        <v>5648800</v>
+        <v>5613800</v>
       </c>
       <c r="G17" s="3">
-        <v>2900700</v>
+        <v>2882800</v>
       </c>
       <c r="H17" s="3">
-        <v>2628000</v>
+        <v>2611800</v>
       </c>
       <c r="I17" s="3">
-        <v>2022300</v>
+        <v>2009800</v>
       </c>
       <c r="J17" s="3">
-        <v>688600</v>
+        <v>684400</v>
       </c>
       <c r="K17" s="3">
         <v>359400</v>
@@ -1122,22 +1123,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3125900</v>
+        <v>-3106500</v>
       </c>
       <c r="E18" s="3">
-        <v>-2155100</v>
+        <v>-2141800</v>
       </c>
       <c r="F18" s="3">
-        <v>-625100</v>
+        <v>-621200</v>
       </c>
       <c r="G18" s="3">
-        <v>-640600</v>
+        <v>-636600</v>
       </c>
       <c r="H18" s="3">
-        <v>-1540200</v>
+        <v>-1530700</v>
       </c>
       <c r="I18" s="3">
-        <v>-1334000</v>
+        <v>-1325700</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1186,22 +1187,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>337800</v>
+        <v>335700</v>
       </c>
       <c r="E20" s="3">
-        <v>202100</v>
+        <v>200800</v>
       </c>
       <c r="F20" s="3">
-        <v>161100</v>
+        <v>160100</v>
       </c>
       <c r="G20" s="3">
-        <v>-36700</v>
+        <v>-36500</v>
       </c>
       <c r="H20" s="3">
-        <v>22500</v>
+        <v>22400</v>
       </c>
       <c r="I20" s="3">
-        <v>14200</v>
+        <v>14100</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1230,23 +1231,23 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-2305200</v>
       </c>
       <c r="E21" s="3">
-        <v>-1556100</v>
+        <v>-1547800</v>
       </c>
       <c r="F21" s="3">
-        <v>-226300</v>
+        <v>-225600</v>
       </c>
       <c r="G21" s="3">
-        <v>-531600</v>
+        <v>-528800</v>
       </c>
       <c r="H21" s="3">
-        <v>-1378700</v>
+        <v>-1370600</v>
       </c>
       <c r="I21" s="3">
-        <v>-1253800</v>
+        <v>-1246200</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1276,22 +1277,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>56100</v>
+        <v>55800</v>
       </c>
       <c r="E22" s="3">
-        <v>46300</v>
+        <v>46000</v>
       </c>
       <c r="F22" s="3">
-        <v>88600</v>
+        <v>88100</v>
       </c>
       <c r="G22" s="3">
-        <v>59200</v>
+        <v>58900</v>
       </c>
       <c r="H22" s="3">
-        <v>51500</v>
+        <v>51200</v>
       </c>
       <c r="I22" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="J22" s="3">
         <v>2500</v>
@@ -1321,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2844200</v>
+        <v>-2826600</v>
       </c>
       <c r="E23" s="3">
-        <v>-1999400</v>
+        <v>-1987000</v>
       </c>
       <c r="F23" s="3">
-        <v>-552600</v>
+        <v>-549100</v>
       </c>
       <c r="G23" s="3">
-        <v>-736500</v>
+        <v>-731900</v>
       </c>
       <c r="H23" s="3">
-        <v>-1569200</v>
+        <v>-1559500</v>
       </c>
       <c r="I23" s="3">
-        <v>-1336900</v>
+        <v>-1328700</v>
       </c>
       <c r="J23" s="3">
-        <v>-696900</v>
+        <v>-692600</v>
       </c>
       <c r="K23" s="3">
         <v>-354700</v>
@@ -1366,13 +1367,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>36300</v>
+        <v>36000</v>
       </c>
       <c r="E24" s="3">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="F24" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="G24" s="3">
         <v>900</v>
@@ -1381,7 +1382,7 @@
         <v>1100</v>
       </c>
       <c r="I24" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="J24" s="3">
         <v>1100</v>
@@ -1456,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2880500</v>
+        <v>-2862600</v>
       </c>
       <c r="E26" s="3">
-        <v>-2007000</v>
+        <v>-1994600</v>
       </c>
       <c r="F26" s="3">
-        <v>-558400</v>
+        <v>-555000</v>
       </c>
       <c r="G26" s="3">
-        <v>-737400</v>
+        <v>-732800</v>
       </c>
       <c r="H26" s="3">
-        <v>-1570300</v>
+        <v>-1560600</v>
       </c>
       <c r="I26" s="3">
-        <v>-1340000</v>
+        <v>-1331700</v>
       </c>
       <c r="J26" s="3">
-        <v>-698000</v>
+        <v>-693700</v>
       </c>
       <c r="K26" s="3">
         <v>-355300</v>
@@ -1501,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2939900</v>
+        <v>-2921700</v>
       </c>
       <c r="E27" s="3">
-        <v>-2024100</v>
+        <v>-2011500</v>
       </c>
       <c r="F27" s="3">
-        <v>-1469800</v>
+        <v>-1460700</v>
       </c>
       <c r="G27" s="3">
-        <v>-780000</v>
+        <v>-775200</v>
       </c>
       <c r="H27" s="3">
-        <v>-1586600</v>
+        <v>-1576800</v>
       </c>
       <c r="I27" s="3">
-        <v>-3243000</v>
+        <v>-3223000</v>
       </c>
       <c r="J27" s="3">
-        <v>-1051200</v>
+        <v>-1044700</v>
       </c>
       <c r="K27" s="3">
         <v>-485700</v>
@@ -1726,22 +1727,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-337800</v>
+        <v>-335700</v>
       </c>
       <c r="E32" s="3">
-        <v>-202100</v>
+        <v>-200800</v>
       </c>
       <c r="F32" s="3">
-        <v>-161100</v>
+        <v>-160100</v>
       </c>
       <c r="G32" s="3">
-        <v>36700</v>
+        <v>36500</v>
       </c>
       <c r="H32" s="3">
-        <v>-22500</v>
+        <v>-22400</v>
       </c>
       <c r="I32" s="3">
-        <v>-14200</v>
+        <v>-14100</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1771,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2939900</v>
+        <v>-2921700</v>
       </c>
       <c r="E33" s="3">
-        <v>-2024100</v>
+        <v>-2011500</v>
       </c>
       <c r="F33" s="3">
-        <v>-1469800</v>
+        <v>-1460700</v>
       </c>
       <c r="G33" s="3">
-        <v>-780000</v>
+        <v>-775200</v>
       </c>
       <c r="H33" s="3">
-        <v>-1586600</v>
+        <v>-1576800</v>
       </c>
       <c r="I33" s="3">
-        <v>-3243000</v>
+        <v>-3223000</v>
       </c>
       <c r="J33" s="3">
-        <v>-1051200</v>
+        <v>-1044700</v>
       </c>
       <c r="K33" s="3">
         <v>-485700</v>
@@ -1861,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2939900</v>
+        <v>-2921700</v>
       </c>
       <c r="E35" s="3">
-        <v>-2024100</v>
+        <v>-2011500</v>
       </c>
       <c r="F35" s="3">
-        <v>-1469800</v>
+        <v>-1460700</v>
       </c>
       <c r="G35" s="3">
-        <v>-780000</v>
+        <v>-775200</v>
       </c>
       <c r="H35" s="3">
-        <v>-1586600</v>
+        <v>-1576800</v>
       </c>
       <c r="I35" s="3">
-        <v>-3243000</v>
+        <v>-3223000</v>
       </c>
       <c r="J35" s="3">
-        <v>-1051200</v>
+        <v>-1044700</v>
       </c>
       <c r="K35" s="3">
         <v>-485700</v>
@@ -1994,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4578600</v>
+        <v>4550300</v>
       </c>
       <c r="E41" s="3">
-        <v>2764800</v>
+        <v>2747700</v>
       </c>
       <c r="F41" s="3">
-        <v>2131700</v>
+        <v>2118500</v>
       </c>
       <c r="G41" s="3">
-        <v>5341900</v>
+        <v>5308900</v>
       </c>
       <c r="H41" s="3">
-        <v>120000</v>
+        <v>119200</v>
       </c>
       <c r="I41" s="3">
-        <v>435700</v>
+        <v>433000</v>
       </c>
       <c r="J41" s="3">
-        <v>1043500</v>
+        <v>1037000</v>
       </c>
       <c r="K41" s="3">
         <v>80300</v>
@@ -2039,22 +2040,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2336900</v>
+        <v>2322500</v>
       </c>
       <c r="E42" s="3">
-        <v>2665200</v>
+        <v>2648700</v>
       </c>
       <c r="F42" s="3">
-        <v>5151700</v>
+        <v>5119900</v>
       </c>
       <c r="G42" s="3">
-        <v>549200</v>
+        <v>545800</v>
       </c>
       <c r="H42" s="3">
-        <v>15400</v>
+        <v>15300</v>
       </c>
       <c r="I42" s="3">
-        <v>716600</v>
+        <v>712200</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -2084,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>887000</v>
+        <v>1216100</v>
       </c>
       <c r="E43" s="3">
-        <v>1030200</v>
+        <v>1023900</v>
       </c>
       <c r="F43" s="3">
-        <v>780100</v>
+        <v>775300</v>
       </c>
       <c r="G43" s="3">
-        <v>333100</v>
+        <v>331000</v>
       </c>
       <c r="H43" s="3">
-        <v>392000</v>
+        <v>389600</v>
       </c>
       <c r="I43" s="3">
-        <v>278300</v>
+        <v>276600</v>
       </c>
       <c r="J43" s="3">
-        <v>70300</v>
+        <v>69900</v>
       </c>
       <c r="K43" s="3">
         <v>25300</v>
@@ -2129,22 +2130,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>733700</v>
+        <v>729200</v>
       </c>
       <c r="E44" s="3">
-        <v>1138800</v>
+        <v>1131700</v>
       </c>
       <c r="F44" s="3">
-        <v>285900</v>
+        <v>284100</v>
       </c>
       <c r="G44" s="3">
-        <v>150400</v>
+        <v>149400</v>
       </c>
       <c r="H44" s="3">
-        <v>123700</v>
+        <v>122900</v>
       </c>
       <c r="I44" s="3">
-        <v>203700</v>
+        <v>202400</v>
       </c>
       <c r="J44" s="3">
         <v>12400</v>
@@ -2174,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1248000</v>
+        <v>905600</v>
       </c>
       <c r="E45" s="3">
-        <v>624100</v>
+        <v>620200</v>
       </c>
       <c r="F45" s="3">
-        <v>498000</v>
+        <v>494900</v>
       </c>
       <c r="G45" s="3">
-        <v>49100</v>
+        <v>48800</v>
       </c>
       <c r="H45" s="3">
-        <v>34000</v>
+        <v>33800</v>
       </c>
       <c r="I45" s="3">
-        <v>57500</v>
+        <v>57200</v>
       </c>
       <c r="J45" s="3">
-        <v>29000</v>
+        <v>28800</v>
       </c>
       <c r="K45" s="3">
         <v>15300</v>
@@ -2219,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9784300</v>
+        <v>9723700</v>
       </c>
       <c r="E46" s="3">
-        <v>8223000</v>
+        <v>8172100</v>
       </c>
       <c r="F46" s="3">
-        <v>8847400</v>
+        <v>8792700</v>
       </c>
       <c r="G46" s="3">
-        <v>6423700</v>
+        <v>6383900</v>
       </c>
       <c r="H46" s="3">
-        <v>685100</v>
+        <v>680900</v>
       </c>
       <c r="I46" s="3">
-        <v>1691800</v>
+        <v>1681400</v>
       </c>
       <c r="J46" s="3">
-        <v>1155300</v>
+        <v>1148100</v>
       </c>
       <c r="K46" s="3">
         <v>120800</v>
@@ -2264,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>762800</v>
+        <v>1109900</v>
       </c>
       <c r="E47" s="3">
-        <v>1710800</v>
+        <v>1700200</v>
       </c>
       <c r="F47" s="3">
-        <v>1051700</v>
+        <v>1045200</v>
       </c>
       <c r="G47" s="3">
-        <v>220900</v>
+        <v>219600</v>
       </c>
       <c r="H47" s="3">
-        <v>107500</v>
+        <v>106800</v>
       </c>
       <c r="I47" s="3">
-        <v>101600</v>
+        <v>101000</v>
       </c>
       <c r="J47" s="3">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2309,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5039600</v>
+        <v>5016200</v>
       </c>
       <c r="E48" s="3">
-        <v>3208900</v>
+        <v>3189100</v>
       </c>
       <c r="F48" s="3">
-        <v>1453300</v>
+        <v>1444300</v>
       </c>
       <c r="G48" s="3">
-        <v>895600</v>
+        <v>890100</v>
       </c>
       <c r="H48" s="3">
-        <v>1068500</v>
+        <v>1061900</v>
       </c>
       <c r="I48" s="3">
-        <v>674700</v>
+        <v>670500</v>
       </c>
       <c r="J48" s="3">
-        <v>265700</v>
+        <v>264000</v>
       </c>
       <c r="K48" s="3">
         <v>115000</v>
@@ -2354,22 +2355,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>32900</v>
+        <v>32700</v>
       </c>
       <c r="E49" s="3">
-        <v>29600</v>
+        <v>29400</v>
       </c>
       <c r="F49" s="3">
-        <v>27700</v>
+        <v>27500</v>
       </c>
       <c r="G49" s="3">
-        <v>28400</v>
+        <v>28300</v>
       </c>
       <c r="H49" s="3">
-        <v>29200</v>
+        <v>29100</v>
       </c>
       <c r="I49" s="3">
-        <v>30200</v>
+        <v>30000</v>
       </c>
       <c r="J49" s="3">
         <v>600</v>
@@ -2489,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>698900</v>
+        <v>335100</v>
       </c>
       <c r="E52" s="3">
-        <v>210400</v>
+        <v>209100</v>
       </c>
       <c r="F52" s="3">
-        <v>142400</v>
+        <v>141500</v>
       </c>
       <c r="G52" s="3">
-        <v>27700</v>
+        <v>27500</v>
       </c>
       <c r="H52" s="3">
-        <v>136900</v>
+        <v>136100</v>
       </c>
       <c r="I52" s="3">
-        <v>121200</v>
+        <v>120400</v>
       </c>
       <c r="J52" s="3">
-        <v>20200</v>
+        <v>20100</v>
       </c>
       <c r="K52" s="3">
         <v>7700</v>
@@ -2579,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16318600</v>
+        <v>16217700</v>
       </c>
       <c r="E54" s="3">
-        <v>13382600</v>
+        <v>13299800</v>
       </c>
       <c r="F54" s="3">
-        <v>11522500</v>
+        <v>11451200</v>
       </c>
       <c r="G54" s="3">
-        <v>7596300</v>
+        <v>7549300</v>
       </c>
       <c r="H54" s="3">
-        <v>2027200</v>
+        <v>2014700</v>
       </c>
       <c r="I54" s="3">
-        <v>2619500</v>
+        <v>2603300</v>
       </c>
       <c r="J54" s="3">
-        <v>1455300</v>
+        <v>1446300</v>
       </c>
       <c r="K54" s="3">
         <v>244500</v>
@@ -2662,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4138100</v>
+        <v>4726700</v>
       </c>
       <c r="E57" s="3">
-        <v>4086700</v>
+        <v>4061400</v>
       </c>
       <c r="F57" s="3">
-        <v>1959900</v>
+        <v>1947700</v>
       </c>
       <c r="G57" s="3">
-        <v>984800</v>
+        <v>978700</v>
       </c>
       <c r="H57" s="3">
-        <v>588500</v>
+        <v>584900</v>
       </c>
       <c r="I57" s="3">
-        <v>541800</v>
+        <v>538500</v>
       </c>
       <c r="J57" s="3">
-        <v>89600</v>
+        <v>89100</v>
       </c>
       <c r="K57" s="3">
         <v>26300</v>
@@ -2707,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1365400</v>
+        <v>1360400</v>
       </c>
       <c r="E58" s="3">
-        <v>737900</v>
+        <v>733300</v>
       </c>
       <c r="F58" s="3">
-        <v>1018400</v>
+        <v>1012100</v>
       </c>
       <c r="G58" s="3">
-        <v>273000</v>
+        <v>271300</v>
       </c>
       <c r="H58" s="3">
-        <v>173600</v>
+        <v>172500</v>
       </c>
       <c r="I58" s="3">
-        <v>287600</v>
+        <v>285800</v>
       </c>
       <c r="J58" s="3">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="K58" s="3">
         <v>2700</v>
@@ -2752,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2531600</v>
+        <v>1898200</v>
       </c>
       <c r="E59" s="3">
-        <v>1549800</v>
+        <v>1540200</v>
       </c>
       <c r="F59" s="3">
-        <v>1080800</v>
+        <v>1074100</v>
       </c>
       <c r="G59" s="3">
-        <v>685200</v>
+        <v>680900</v>
       </c>
       <c r="H59" s="3">
-        <v>558500</v>
+        <v>555000</v>
       </c>
       <c r="I59" s="3">
-        <v>365200</v>
+        <v>363000</v>
       </c>
       <c r="J59" s="3">
-        <v>123700</v>
+        <v>123000</v>
       </c>
       <c r="K59" s="3">
         <v>71300</v>
@@ -2797,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8035100</v>
+        <v>7985400</v>
       </c>
       <c r="E60" s="3">
-        <v>6374400</v>
+        <v>6334900</v>
       </c>
       <c r="F60" s="3">
-        <v>4059100</v>
+        <v>4034000</v>
       </c>
       <c r="G60" s="3">
-        <v>1943000</v>
+        <v>1931000</v>
       </c>
       <c r="H60" s="3">
-        <v>1320500</v>
+        <v>1312400</v>
       </c>
       <c r="I60" s="3">
-        <v>1194700</v>
+        <v>1187300</v>
       </c>
       <c r="J60" s="3">
-        <v>225000</v>
+        <v>223600</v>
       </c>
       <c r="K60" s="3">
         <v>100300</v>
@@ -2842,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1813200</v>
+        <v>1805100</v>
       </c>
       <c r="E61" s="3">
-        <v>1515400</v>
+        <v>1506000</v>
       </c>
       <c r="F61" s="3">
-        <v>1358300</v>
+        <v>1349900</v>
       </c>
       <c r="G61" s="3">
-        <v>833200</v>
+        <v>828000</v>
       </c>
       <c r="H61" s="3">
-        <v>1007000</v>
+        <v>1000800</v>
       </c>
       <c r="I61" s="3">
-        <v>162400</v>
+        <v>161400</v>
       </c>
       <c r="J61" s="3">
-        <v>89300</v>
+        <v>88800</v>
       </c>
       <c r="K61" s="3">
         <v>5200</v>
@@ -2887,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2355900</v>
+        <v>2338200</v>
       </c>
       <c r="E62" s="3">
-        <v>1649500</v>
+        <v>1639200</v>
       </c>
       <c r="F62" s="3">
-        <v>813400</v>
+        <v>808400</v>
       </c>
       <c r="G62" s="3">
-        <v>390700</v>
+        <v>388200</v>
       </c>
       <c r="H62" s="3">
-        <v>370000</v>
+        <v>367700</v>
       </c>
       <c r="I62" s="3">
-        <v>129400</v>
+        <v>128600</v>
       </c>
       <c r="J62" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="K62" s="3">
         <v>8500</v>
@@ -3067,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12767200</v>
+        <v>12688200</v>
       </c>
       <c r="E66" s="3">
-        <v>10064500</v>
+        <v>10002200</v>
       </c>
       <c r="F66" s="3">
-        <v>6697100</v>
+        <v>6655700</v>
       </c>
       <c r="G66" s="3">
-        <v>3819300</v>
+        <v>3795700</v>
       </c>
       <c r="H66" s="3">
-        <v>2903000</v>
+        <v>2885000</v>
       </c>
       <c r="I66" s="3">
-        <v>1669000</v>
+        <v>1658700</v>
       </c>
       <c r="J66" s="3">
-        <v>335500</v>
+        <v>333400</v>
       </c>
       <c r="K66" s="3">
         <v>112400</v>
@@ -3239,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>2732800</v>
+        <v>2715900</v>
       </c>
       <c r="K70" s="3">
         <v>671300</v>
@@ -3310,26 +3311,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-12539100</v>
       </c>
       <c r="E72" s="3">
-        <v>-9719500</v>
+        <v>-9659400</v>
       </c>
       <c r="F72" s="3">
-        <v>-7734300</v>
+        <v>-7686400</v>
       </c>
       <c r="G72" s="3">
-        <v>-7180200</v>
+        <v>-7135700</v>
       </c>
       <c r="H72" s="3">
-        <v>-6440300</v>
+        <v>-6400400</v>
       </c>
       <c r="I72" s="3">
-        <v>-4871200</v>
+        <v>-4841100</v>
       </c>
       <c r="J72" s="3">
-        <v>-1628200</v>
+        <v>-1618100</v>
       </c>
       <c r="K72" s="3">
         <v>-562900</v>
@@ -3491,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3551400</v>
+        <v>3529500</v>
       </c>
       <c r="E76" s="3">
-        <v>3318200</v>
+        <v>3297600</v>
       </c>
       <c r="F76" s="3">
-        <v>4825400</v>
+        <v>4795500</v>
       </c>
       <c r="G76" s="3">
-        <v>3777000</v>
+        <v>3753600</v>
       </c>
       <c r="H76" s="3">
-        <v>-875800</v>
+        <v>-870400</v>
       </c>
       <c r="I76" s="3">
-        <v>950500</v>
+        <v>944600</v>
       </c>
       <c r="J76" s="3">
-        <v>-1613000</v>
+        <v>-1603100</v>
       </c>
       <c r="K76" s="3">
         <v>-539200</v>
@@ -3631,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2939900</v>
+        <v>-2921700</v>
       </c>
       <c r="E81" s="3">
-        <v>-2024100</v>
+        <v>-2011500</v>
       </c>
       <c r="F81" s="3">
-        <v>-1469800</v>
+        <v>-1460700</v>
       </c>
       <c r="G81" s="3">
-        <v>-780000</v>
+        <v>-775200</v>
       </c>
       <c r="H81" s="3">
-        <v>-1586600</v>
+        <v>-1576800</v>
       </c>
       <c r="I81" s="3">
-        <v>-3243000</v>
+        <v>-3223000</v>
       </c>
       <c r="J81" s="3">
-        <v>-1051200</v>
+        <v>-1044700</v>
       </c>
       <c r="K81" s="3">
         <v>-485700</v>
@@ -3694,26 +3695,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>466700</v>
       </c>
       <c r="E83" s="3">
-        <v>396500</v>
+        <v>394100</v>
       </c>
       <c r="F83" s="3">
-        <v>237400</v>
+        <v>236000</v>
       </c>
       <c r="G83" s="3">
-        <v>145500</v>
+        <v>144600</v>
       </c>
       <c r="H83" s="3">
-        <v>138900</v>
+        <v>138000</v>
       </c>
       <c r="I83" s="3">
-        <v>65900</v>
+        <v>65500</v>
       </c>
       <c r="J83" s="3">
-        <v>23300</v>
+        <v>23200</v>
       </c>
       <c r="K83" s="3">
         <v>6400</v>
@@ -3964,26 +3965,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-190900</v>
       </c>
       <c r="E89" s="3">
-        <v>-537500</v>
+        <v>-534100</v>
       </c>
       <c r="F89" s="3">
-        <v>273400</v>
+        <v>271700</v>
       </c>
       <c r="G89" s="3">
-        <v>271200</v>
+        <v>269500</v>
       </c>
       <c r="H89" s="3">
-        <v>-1212500</v>
+        <v>-1205000</v>
       </c>
       <c r="I89" s="3">
-        <v>-1099900</v>
+        <v>-1093100</v>
       </c>
       <c r="J89" s="3">
-        <v>-636000</v>
+        <v>-632000</v>
       </c>
       <c r="K89" s="3">
         <v>-304000</v>
@@ -4028,26 +4029,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-1981300</v>
       </c>
       <c r="E91" s="3">
-        <v>-969400</v>
+        <v>-963400</v>
       </c>
       <c r="F91" s="3">
-        <v>-567000</v>
+        <v>-563500</v>
       </c>
       <c r="G91" s="3">
-        <v>-156800</v>
+        <v>-155800</v>
       </c>
       <c r="H91" s="3">
-        <v>-237300</v>
+        <v>-235800</v>
       </c>
       <c r="I91" s="3">
-        <v>-367600</v>
+        <v>-365300</v>
       </c>
       <c r="J91" s="3">
-        <v>-154900</v>
+        <v>-153900</v>
       </c>
       <c r="K91" s="3">
         <v>-90400</v>
@@ -4163,26 +4164,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-1503900</v>
       </c>
       <c r="E94" s="3">
-        <v>1443700</v>
+        <v>1434800</v>
       </c>
       <c r="F94" s="3">
-        <v>-5528100</v>
+        <v>-5493900</v>
       </c>
       <c r="G94" s="3">
-        <v>-705000</v>
+        <v>-700600</v>
       </c>
       <c r="H94" s="3">
-        <v>470200</v>
+        <v>467300</v>
       </c>
       <c r="I94" s="3">
-        <v>-1103900</v>
+        <v>-1097100</v>
       </c>
       <c r="J94" s="3">
-        <v>-165500</v>
+        <v>-164400</v>
       </c>
       <c r="K94" s="3">
         <v>16300</v>
@@ -4407,26 +4408,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>3821900</v>
       </c>
       <c r="E100" s="3">
-        <v>-224700</v>
+        <v>-223300</v>
       </c>
       <c r="F100" s="3">
-        <v>2520300</v>
+        <v>2504700</v>
       </c>
       <c r="G100" s="3">
-        <v>5749500</v>
+        <v>5713900</v>
       </c>
       <c r="H100" s="3">
-        <v>430300</v>
+        <v>427600</v>
       </c>
       <c r="I100" s="3">
-        <v>1613100</v>
+        <v>1603100</v>
       </c>
       <c r="J100" s="3">
-        <v>1788800</v>
+        <v>1777800</v>
       </c>
       <c r="K100" s="3">
         <v>316600</v>
@@ -4452,17 +4453,17 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>9700</v>
       </c>
       <c r="E101" s="3">
-        <v>-16900</v>
+        <v>-16800</v>
       </c>
       <c r="F101" s="3">
-        <v>-69600</v>
+        <v>-69200</v>
       </c>
       <c r="G101" s="3">
-        <v>-94800</v>
+        <v>-94200</v>
       </c>
       <c r="H101" s="3">
         <v>1400</v>
@@ -4471,7 +4472,7 @@
         <v>-7900</v>
       </c>
       <c r="J101" s="3">
-        <v>-23400</v>
+        <v>-23200</v>
       </c>
       <c r="K101" s="3">
         <v>5600</v>
@@ -4497,26 +4498,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>2136800</v>
       </c>
       <c r="E102" s="3">
-        <v>664600</v>
+        <v>660500</v>
       </c>
       <c r="F102" s="3">
-        <v>-2804100</v>
+        <v>-2786800</v>
       </c>
       <c r="G102" s="3">
-        <v>5220900</v>
+        <v>5188600</v>
       </c>
       <c r="H102" s="3">
-        <v>-310600</v>
+        <v>-308700</v>
       </c>
       <c r="I102" s="3">
-        <v>-598700</v>
+        <v>-595000</v>
       </c>
       <c r="J102" s="3">
-        <v>964000</v>
+        <v>958000</v>
       </c>
       <c r="K102" s="3">
         <v>34500</v>

--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -728,22 +728,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>7684200</v>
+        <v>7841000</v>
       </c>
       <c r="E8" s="3">
-        <v>6806900</v>
+        <v>6945900</v>
       </c>
       <c r="F8" s="3">
-        <v>4992600</v>
+        <v>5094500</v>
       </c>
       <c r="G8" s="3">
-        <v>2246200</v>
+        <v>2292000</v>
       </c>
       <c r="H8" s="3">
-        <v>1081100</v>
+        <v>1103200</v>
       </c>
       <c r="I8" s="3">
-        <v>684100</v>
+        <v>698000</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -773,22 +773,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>7262500</v>
+        <v>7410800</v>
       </c>
       <c r="E9" s="3">
-        <v>6096300</v>
+        <v>6220700</v>
       </c>
       <c r="F9" s="3">
-        <v>4050200</v>
+        <v>4132800</v>
       </c>
       <c r="G9" s="3">
-        <v>1987400</v>
+        <v>2027900</v>
       </c>
       <c r="H9" s="3">
-        <v>1246700</v>
+        <v>1272200</v>
       </c>
       <c r="I9" s="3">
-        <v>719400</v>
+        <v>734100</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -818,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>421600</v>
+        <v>430200</v>
       </c>
       <c r="E10" s="3">
-        <v>710700</v>
+        <v>725200</v>
       </c>
       <c r="F10" s="3">
-        <v>942400</v>
+        <v>961700</v>
       </c>
       <c r="G10" s="3">
-        <v>258800</v>
+        <v>264100</v>
       </c>
       <c r="H10" s="3">
-        <v>-165600</v>
+        <v>-169000</v>
       </c>
       <c r="I10" s="3">
-        <v>-35400</v>
+        <v>-36100</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -882,25 +882,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1756100</v>
+        <v>1791900</v>
       </c>
       <c r="E12" s="3">
-        <v>1451100</v>
+        <v>1480700</v>
       </c>
       <c r="F12" s="3">
-        <v>604800</v>
+        <v>617100</v>
       </c>
       <c r="G12" s="3">
-        <v>308400</v>
+        <v>314700</v>
       </c>
       <c r="H12" s="3">
-        <v>586000</v>
+        <v>598000</v>
       </c>
       <c r="I12" s="3">
-        <v>538100</v>
+        <v>549000</v>
       </c>
       <c r="J12" s="3">
-        <v>354200</v>
+        <v>361500</v>
       </c>
       <c r="K12" s="3">
         <v>201300</v>
@@ -972,10 +972,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-23500</v>
+        <v>-24000</v>
       </c>
       <c r="E14" s="3">
-        <v>-19100</v>
+        <v>-19500</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>192500</v>
+        <v>196400</v>
       </c>
       <c r="E15" s="3">
-        <v>112900</v>
+        <v>115200</v>
       </c>
       <c r="F15" s="3">
-        <v>76300</v>
+        <v>77800</v>
       </c>
       <c r="G15" s="3">
-        <v>80300</v>
+        <v>81900</v>
       </c>
       <c r="H15" s="3">
-        <v>89000</v>
+        <v>90900</v>
       </c>
       <c r="I15" s="3">
-        <v>48800</v>
+        <v>49800</v>
       </c>
       <c r="J15" s="3">
-        <v>23200</v>
+        <v>23700</v>
       </c>
       <c r="K15" s="3">
         <v>6400</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10790700</v>
+        <v>11011000</v>
       </c>
       <c r="E17" s="3">
-        <v>8948700</v>
+        <v>9131400</v>
       </c>
       <c r="F17" s="3">
-        <v>5613800</v>
+        <v>5728400</v>
       </c>
       <c r="G17" s="3">
-        <v>2882800</v>
+        <v>2941600</v>
       </c>
       <c r="H17" s="3">
-        <v>2611800</v>
+        <v>2665100</v>
       </c>
       <c r="I17" s="3">
-        <v>2009800</v>
+        <v>2050800</v>
       </c>
       <c r="J17" s="3">
-        <v>684400</v>
+        <v>698400</v>
       </c>
       <c r="K17" s="3">
         <v>359400</v>
@@ -1123,22 +1123,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3106500</v>
+        <v>-3169900</v>
       </c>
       <c r="E18" s="3">
-        <v>-2141800</v>
+        <v>-2185500</v>
       </c>
       <c r="F18" s="3">
-        <v>-621200</v>
+        <v>-633900</v>
       </c>
       <c r="G18" s="3">
-        <v>-636600</v>
+        <v>-649600</v>
       </c>
       <c r="H18" s="3">
-        <v>-1530700</v>
+        <v>-1561900</v>
       </c>
       <c r="I18" s="3">
-        <v>-1325700</v>
+        <v>-1352800</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1187,22 +1187,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>335700</v>
+        <v>342500</v>
       </c>
       <c r="E20" s="3">
-        <v>200800</v>
+        <v>204900</v>
       </c>
       <c r="F20" s="3">
-        <v>160100</v>
+        <v>163400</v>
       </c>
       <c r="G20" s="3">
-        <v>-36500</v>
+        <v>-37200</v>
       </c>
       <c r="H20" s="3">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="I20" s="3">
-        <v>14100</v>
+        <v>14400</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1232,22 +1232,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2305200</v>
+        <v>-2352800</v>
       </c>
       <c r="E21" s="3">
-        <v>-1547800</v>
+        <v>-1579800</v>
       </c>
       <c r="F21" s="3">
-        <v>-225600</v>
+        <v>-230500</v>
       </c>
       <c r="G21" s="3">
-        <v>-528800</v>
+        <v>-539800</v>
       </c>
       <c r="H21" s="3">
-        <v>-1370600</v>
+        <v>-1398800</v>
       </c>
       <c r="I21" s="3">
-        <v>-1246200</v>
+        <v>-1271700</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1277,22 +1277,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>55800</v>
+        <v>56900</v>
       </c>
       <c r="E22" s="3">
-        <v>46000</v>
+        <v>47000</v>
       </c>
       <c r="F22" s="3">
-        <v>88100</v>
+        <v>89900</v>
       </c>
       <c r="G22" s="3">
-        <v>58900</v>
+        <v>60100</v>
       </c>
       <c r="H22" s="3">
-        <v>51200</v>
+        <v>52200</v>
       </c>
       <c r="I22" s="3">
-        <v>17100</v>
+        <v>17400</v>
       </c>
       <c r="J22" s="3">
         <v>2500</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2826600</v>
+        <v>-2884300</v>
       </c>
       <c r="E23" s="3">
-        <v>-1987000</v>
+        <v>-2027600</v>
       </c>
       <c r="F23" s="3">
-        <v>-549100</v>
+        <v>-560400</v>
       </c>
       <c r="G23" s="3">
-        <v>-731900</v>
+        <v>-746900</v>
       </c>
       <c r="H23" s="3">
-        <v>-1559500</v>
+        <v>-1591300</v>
       </c>
       <c r="I23" s="3">
-        <v>-1328700</v>
+        <v>-1355800</v>
       </c>
       <c r="J23" s="3">
-        <v>-692600</v>
+        <v>-706800</v>
       </c>
       <c r="K23" s="3">
         <v>-354700</v>
@@ -1367,13 +1367,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>36000</v>
+        <v>36800</v>
       </c>
       <c r="E24" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="F24" s="3">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="G24" s="3">
         <v>900</v>
@@ -1382,7 +1382,7 @@
         <v>1100</v>
       </c>
       <c r="I24" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="J24" s="3">
         <v>1100</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2862600</v>
+        <v>-2921100</v>
       </c>
       <c r="E26" s="3">
-        <v>-1994600</v>
+        <v>-2035300</v>
       </c>
       <c r="F26" s="3">
-        <v>-555000</v>
+        <v>-566300</v>
       </c>
       <c r="G26" s="3">
-        <v>-732800</v>
+        <v>-747800</v>
       </c>
       <c r="H26" s="3">
-        <v>-1560600</v>
+        <v>-1592500</v>
       </c>
       <c r="I26" s="3">
-        <v>-1331700</v>
+        <v>-1358900</v>
       </c>
       <c r="J26" s="3">
-        <v>-693700</v>
+        <v>-707900</v>
       </c>
       <c r="K26" s="3">
         <v>-355300</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2921700</v>
+        <v>-2981300</v>
       </c>
       <c r="E27" s="3">
-        <v>-2011500</v>
+        <v>-2052600</v>
       </c>
       <c r="F27" s="3">
-        <v>-1460700</v>
+        <v>-1490500</v>
       </c>
       <c r="G27" s="3">
-        <v>-775200</v>
+        <v>-791000</v>
       </c>
       <c r="H27" s="3">
-        <v>-1576800</v>
+        <v>-1609000</v>
       </c>
       <c r="I27" s="3">
-        <v>-3223000</v>
+        <v>-3288800</v>
       </c>
       <c r="J27" s="3">
-        <v>-1044700</v>
+        <v>-1066000</v>
       </c>
       <c r="K27" s="3">
         <v>-485700</v>
@@ -1727,22 +1727,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-335700</v>
+        <v>-342500</v>
       </c>
       <c r="E32" s="3">
-        <v>-200800</v>
+        <v>-204900</v>
       </c>
       <c r="F32" s="3">
-        <v>-160100</v>
+        <v>-163400</v>
       </c>
       <c r="G32" s="3">
-        <v>36500</v>
+        <v>37200</v>
       </c>
       <c r="H32" s="3">
-        <v>-22400</v>
+        <v>-22800</v>
       </c>
       <c r="I32" s="3">
-        <v>-14100</v>
+        <v>-14400</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2921700</v>
+        <v>-2981300</v>
       </c>
       <c r="E33" s="3">
-        <v>-2011500</v>
+        <v>-2052600</v>
       </c>
       <c r="F33" s="3">
-        <v>-1460700</v>
+        <v>-1490500</v>
       </c>
       <c r="G33" s="3">
-        <v>-775200</v>
+        <v>-791000</v>
       </c>
       <c r="H33" s="3">
-        <v>-1576800</v>
+        <v>-1609000</v>
       </c>
       <c r="I33" s="3">
-        <v>-3223000</v>
+        <v>-3288800</v>
       </c>
       <c r="J33" s="3">
-        <v>-1044700</v>
+        <v>-1066000</v>
       </c>
       <c r="K33" s="3">
         <v>-485700</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2921700</v>
+        <v>-2981300</v>
       </c>
       <c r="E35" s="3">
-        <v>-2011500</v>
+        <v>-2052600</v>
       </c>
       <c r="F35" s="3">
-        <v>-1460700</v>
+        <v>-1490500</v>
       </c>
       <c r="G35" s="3">
-        <v>-775200</v>
+        <v>-791000</v>
       </c>
       <c r="H35" s="3">
-        <v>-1576800</v>
+        <v>-1609000</v>
       </c>
       <c r="I35" s="3">
-        <v>-3223000</v>
+        <v>-3288800</v>
       </c>
       <c r="J35" s="3">
-        <v>-1044700</v>
+        <v>-1066000</v>
       </c>
       <c r="K35" s="3">
         <v>-485700</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4550300</v>
+        <v>4643200</v>
       </c>
       <c r="E41" s="3">
-        <v>2747700</v>
+        <v>2803800</v>
       </c>
       <c r="F41" s="3">
-        <v>2118500</v>
+        <v>2161700</v>
       </c>
       <c r="G41" s="3">
-        <v>5308900</v>
+        <v>5417200</v>
       </c>
       <c r="H41" s="3">
-        <v>119200</v>
+        <v>121600</v>
       </c>
       <c r="I41" s="3">
-        <v>433000</v>
+        <v>441800</v>
       </c>
       <c r="J41" s="3">
-        <v>1037000</v>
+        <v>1058200</v>
       </c>
       <c r="K41" s="3">
         <v>80300</v>
@@ -2040,22 +2040,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2322500</v>
+        <v>2369900</v>
       </c>
       <c r="E42" s="3">
-        <v>2648700</v>
+        <v>2702700</v>
       </c>
       <c r="F42" s="3">
-        <v>5119900</v>
+        <v>5224400</v>
       </c>
       <c r="G42" s="3">
-        <v>545800</v>
+        <v>557000</v>
       </c>
       <c r="H42" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="I42" s="3">
-        <v>712200</v>
+        <v>726700</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1216100</v>
+        <v>1240900</v>
       </c>
       <c r="E43" s="3">
-        <v>1023900</v>
+        <v>1044800</v>
       </c>
       <c r="F43" s="3">
-        <v>775300</v>
+        <v>791100</v>
       </c>
       <c r="G43" s="3">
-        <v>331000</v>
+        <v>337800</v>
       </c>
       <c r="H43" s="3">
-        <v>389600</v>
+        <v>397600</v>
       </c>
       <c r="I43" s="3">
-        <v>276600</v>
+        <v>282300</v>
       </c>
       <c r="J43" s="3">
-        <v>69900</v>
+        <v>71300</v>
       </c>
       <c r="K43" s="3">
         <v>25300</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>729200</v>
+        <v>744100</v>
       </c>
       <c r="E44" s="3">
-        <v>1131700</v>
+        <v>1154800</v>
       </c>
       <c r="F44" s="3">
-        <v>284100</v>
+        <v>289900</v>
       </c>
       <c r="G44" s="3">
-        <v>149400</v>
+        <v>152500</v>
       </c>
       <c r="H44" s="3">
-        <v>122900</v>
+        <v>125400</v>
       </c>
       <c r="I44" s="3">
-        <v>202400</v>
+        <v>206600</v>
       </c>
       <c r="J44" s="3">
-        <v>12400</v>
+        <v>12600</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>905600</v>
+        <v>924100</v>
       </c>
       <c r="E45" s="3">
-        <v>620200</v>
+        <v>632900</v>
       </c>
       <c r="F45" s="3">
-        <v>494900</v>
+        <v>505000</v>
       </c>
       <c r="G45" s="3">
-        <v>48800</v>
+        <v>49800</v>
       </c>
       <c r="H45" s="3">
-        <v>33800</v>
+        <v>34500</v>
       </c>
       <c r="I45" s="3">
-        <v>57200</v>
+        <v>58300</v>
       </c>
       <c r="J45" s="3">
-        <v>28800</v>
+        <v>29400</v>
       </c>
       <c r="K45" s="3">
         <v>15300</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9723700</v>
+        <v>9922200</v>
       </c>
       <c r="E46" s="3">
-        <v>8172100</v>
+        <v>8338900</v>
       </c>
       <c r="F46" s="3">
-        <v>8792700</v>
+        <v>8972200</v>
       </c>
       <c r="G46" s="3">
-        <v>6383900</v>
+        <v>6514200</v>
       </c>
       <c r="H46" s="3">
-        <v>680900</v>
+        <v>694800</v>
       </c>
       <c r="I46" s="3">
-        <v>1681400</v>
+        <v>1715700</v>
       </c>
       <c r="J46" s="3">
-        <v>1148100</v>
+        <v>1171500</v>
       </c>
       <c r="K46" s="3">
         <v>120800</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1109900</v>
+        <v>1132500</v>
       </c>
       <c r="E47" s="3">
-        <v>1700200</v>
+        <v>1734900</v>
       </c>
       <c r="F47" s="3">
-        <v>1045200</v>
+        <v>1066500</v>
       </c>
       <c r="G47" s="3">
-        <v>219600</v>
+        <v>224000</v>
       </c>
       <c r="H47" s="3">
-        <v>106800</v>
+        <v>109000</v>
       </c>
       <c r="I47" s="3">
-        <v>101000</v>
+        <v>103000</v>
       </c>
       <c r="J47" s="3">
-        <v>13400</v>
+        <v>13700</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5016200</v>
+        <v>5118600</v>
       </c>
       <c r="E48" s="3">
-        <v>3189100</v>
+        <v>3254100</v>
       </c>
       <c r="F48" s="3">
-        <v>1444300</v>
+        <v>1473800</v>
       </c>
       <c r="G48" s="3">
-        <v>890100</v>
+        <v>908300</v>
       </c>
       <c r="H48" s="3">
-        <v>1061900</v>
+        <v>1083500</v>
       </c>
       <c r="I48" s="3">
-        <v>670500</v>
+        <v>684200</v>
       </c>
       <c r="J48" s="3">
-        <v>264000</v>
+        <v>269400</v>
       </c>
       <c r="K48" s="3">
         <v>115000</v>
@@ -2355,22 +2355,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>32700</v>
+        <v>33400</v>
       </c>
       <c r="E49" s="3">
-        <v>29400</v>
+        <v>30000</v>
       </c>
       <c r="F49" s="3">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="G49" s="3">
-        <v>28300</v>
+        <v>28800</v>
       </c>
       <c r="H49" s="3">
-        <v>29100</v>
+        <v>29700</v>
       </c>
       <c r="I49" s="3">
-        <v>30000</v>
+        <v>30600</v>
       </c>
       <c r="J49" s="3">
         <v>600</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>335100</v>
+        <v>342000</v>
       </c>
       <c r="E52" s="3">
-        <v>209100</v>
+        <v>213300</v>
       </c>
       <c r="F52" s="3">
-        <v>141500</v>
+        <v>144400</v>
       </c>
       <c r="G52" s="3">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="H52" s="3">
-        <v>136100</v>
+        <v>138800</v>
       </c>
       <c r="I52" s="3">
-        <v>120400</v>
+        <v>122900</v>
       </c>
       <c r="J52" s="3">
-        <v>20100</v>
+        <v>20500</v>
       </c>
       <c r="K52" s="3">
         <v>7700</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16217700</v>
+        <v>16548700</v>
       </c>
       <c r="E54" s="3">
-        <v>13299800</v>
+        <v>13571300</v>
       </c>
       <c r="F54" s="3">
-        <v>11451200</v>
+        <v>11684900</v>
       </c>
       <c r="G54" s="3">
-        <v>7549300</v>
+        <v>7703400</v>
       </c>
       <c r="H54" s="3">
-        <v>2014700</v>
+        <v>2055800</v>
       </c>
       <c r="I54" s="3">
-        <v>2603300</v>
+        <v>2656400</v>
       </c>
       <c r="J54" s="3">
-        <v>1446300</v>
+        <v>1475800</v>
       </c>
       <c r="K54" s="3">
         <v>244500</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4726700</v>
+        <v>4823200</v>
       </c>
       <c r="E57" s="3">
-        <v>4061400</v>
+        <v>4144300</v>
       </c>
       <c r="F57" s="3">
-        <v>1947700</v>
+        <v>1987500</v>
       </c>
       <c r="G57" s="3">
-        <v>978700</v>
+        <v>998700</v>
       </c>
       <c r="H57" s="3">
-        <v>584900</v>
+        <v>596800</v>
       </c>
       <c r="I57" s="3">
-        <v>538500</v>
+        <v>549400</v>
       </c>
       <c r="J57" s="3">
-        <v>89100</v>
+        <v>90900</v>
       </c>
       <c r="K57" s="3">
         <v>26300</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1360400</v>
+        <v>1388200</v>
       </c>
       <c r="E58" s="3">
-        <v>733300</v>
+        <v>748300</v>
       </c>
       <c r="F58" s="3">
-        <v>1012100</v>
+        <v>1032800</v>
       </c>
       <c r="G58" s="3">
-        <v>271300</v>
+        <v>276900</v>
       </c>
       <c r="H58" s="3">
-        <v>172500</v>
+        <v>176000</v>
       </c>
       <c r="I58" s="3">
-        <v>285800</v>
+        <v>291700</v>
       </c>
       <c r="J58" s="3">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="K58" s="3">
         <v>2700</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1898200</v>
+        <v>1937000</v>
       </c>
       <c r="E59" s="3">
-        <v>1540200</v>
+        <v>1571600</v>
       </c>
       <c r="F59" s="3">
-        <v>1074100</v>
+        <v>1096100</v>
       </c>
       <c r="G59" s="3">
-        <v>680900</v>
+        <v>694800</v>
       </c>
       <c r="H59" s="3">
-        <v>555000</v>
+        <v>566300</v>
       </c>
       <c r="I59" s="3">
-        <v>363000</v>
+        <v>370400</v>
       </c>
       <c r="J59" s="3">
-        <v>123000</v>
+        <v>125500</v>
       </c>
       <c r="K59" s="3">
         <v>71300</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7985400</v>
+        <v>8148400</v>
       </c>
       <c r="E60" s="3">
-        <v>6334900</v>
+        <v>6464200</v>
       </c>
       <c r="F60" s="3">
-        <v>4034000</v>
+        <v>4116400</v>
       </c>
       <c r="G60" s="3">
-        <v>1931000</v>
+        <v>1970400</v>
       </c>
       <c r="H60" s="3">
-        <v>1312400</v>
+        <v>1339100</v>
       </c>
       <c r="I60" s="3">
-        <v>1187300</v>
+        <v>1211500</v>
       </c>
       <c r="J60" s="3">
-        <v>223600</v>
+        <v>228200</v>
       </c>
       <c r="K60" s="3">
         <v>100300</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1805100</v>
+        <v>1841900</v>
       </c>
       <c r="E61" s="3">
-        <v>1506000</v>
+        <v>1536700</v>
       </c>
       <c r="F61" s="3">
-        <v>1349900</v>
+        <v>1377500</v>
       </c>
       <c r="G61" s="3">
-        <v>828000</v>
+        <v>844900</v>
       </c>
       <c r="H61" s="3">
-        <v>1000800</v>
+        <v>1021200</v>
       </c>
       <c r="I61" s="3">
-        <v>161400</v>
+        <v>164700</v>
       </c>
       <c r="J61" s="3">
-        <v>88800</v>
+        <v>90600</v>
       </c>
       <c r="K61" s="3">
         <v>5200</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2338200</v>
+        <v>2386000</v>
       </c>
       <c r="E62" s="3">
-        <v>1639200</v>
+        <v>1672700</v>
       </c>
       <c r="F62" s="3">
-        <v>808400</v>
+        <v>824900</v>
       </c>
       <c r="G62" s="3">
-        <v>388200</v>
+        <v>396200</v>
       </c>
       <c r="H62" s="3">
-        <v>367700</v>
+        <v>375200</v>
       </c>
       <c r="I62" s="3">
-        <v>128600</v>
+        <v>131200</v>
       </c>
       <c r="J62" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="K62" s="3">
         <v>8500</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12688200</v>
+        <v>12947200</v>
       </c>
       <c r="E66" s="3">
-        <v>10002200</v>
+        <v>10206400</v>
       </c>
       <c r="F66" s="3">
-        <v>6655700</v>
+        <v>6791500</v>
       </c>
       <c r="G66" s="3">
-        <v>3795700</v>
+        <v>3873200</v>
       </c>
       <c r="H66" s="3">
-        <v>2885000</v>
+        <v>2943900</v>
       </c>
       <c r="I66" s="3">
-        <v>1658700</v>
+        <v>1692500</v>
       </c>
       <c r="J66" s="3">
-        <v>333400</v>
+        <v>340200</v>
       </c>
       <c r="K66" s="3">
         <v>112400</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>2715900</v>
+        <v>2771400</v>
       </c>
       <c r="K70" s="3">
         <v>671300</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-12539100</v>
+        <v>-12795100</v>
       </c>
       <c r="E72" s="3">
-        <v>-9659400</v>
+        <v>-9856500</v>
       </c>
       <c r="F72" s="3">
-        <v>-7686400</v>
+        <v>-7843300</v>
       </c>
       <c r="G72" s="3">
-        <v>-7135700</v>
+        <v>-7281400</v>
       </c>
       <c r="H72" s="3">
-        <v>-6400400</v>
+        <v>-6531100</v>
       </c>
       <c r="I72" s="3">
-        <v>-4841100</v>
+        <v>-4939900</v>
       </c>
       <c r="J72" s="3">
-        <v>-1618100</v>
+        <v>-1651200</v>
       </c>
       <c r="K72" s="3">
         <v>-562900</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3529500</v>
+        <v>3601500</v>
       </c>
       <c r="E76" s="3">
-        <v>3297600</v>
+        <v>3364900</v>
       </c>
       <c r="F76" s="3">
-        <v>4795500</v>
+        <v>4893400</v>
       </c>
       <c r="G76" s="3">
-        <v>3753600</v>
+        <v>3830300</v>
       </c>
       <c r="H76" s="3">
-        <v>-870400</v>
+        <v>-888100</v>
       </c>
       <c r="I76" s="3">
-        <v>944600</v>
+        <v>963900</v>
       </c>
       <c r="J76" s="3">
-        <v>-1603100</v>
+        <v>-1635800</v>
       </c>
       <c r="K76" s="3">
         <v>-539200</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2921700</v>
+        <v>-2981300</v>
       </c>
       <c r="E81" s="3">
-        <v>-2011500</v>
+        <v>-2052600</v>
       </c>
       <c r="F81" s="3">
-        <v>-1460700</v>
+        <v>-1490500</v>
       </c>
       <c r="G81" s="3">
-        <v>-775200</v>
+        <v>-791000</v>
       </c>
       <c r="H81" s="3">
-        <v>-1576800</v>
+        <v>-1609000</v>
       </c>
       <c r="I81" s="3">
-        <v>-3223000</v>
+        <v>-3288800</v>
       </c>
       <c r="J81" s="3">
-        <v>-1044700</v>
+        <v>-1066000</v>
       </c>
       <c r="K81" s="3">
         <v>-485700</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>466700</v>
+        <v>476200</v>
       </c>
       <c r="E83" s="3">
-        <v>394100</v>
+        <v>402100</v>
       </c>
       <c r="F83" s="3">
-        <v>236000</v>
+        <v>240800</v>
       </c>
       <c r="G83" s="3">
-        <v>144600</v>
+        <v>147500</v>
       </c>
       <c r="H83" s="3">
-        <v>138000</v>
+        <v>140800</v>
       </c>
       <c r="I83" s="3">
-        <v>65500</v>
+        <v>66900</v>
       </c>
       <c r="J83" s="3">
-        <v>23200</v>
+        <v>23700</v>
       </c>
       <c r="K83" s="3">
         <v>6400</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-190900</v>
+        <v>-194800</v>
       </c>
       <c r="E89" s="3">
-        <v>-534100</v>
+        <v>-545000</v>
       </c>
       <c r="F89" s="3">
-        <v>271700</v>
+        <v>277200</v>
       </c>
       <c r="G89" s="3">
-        <v>269500</v>
+        <v>275000</v>
       </c>
       <c r="H89" s="3">
-        <v>-1205000</v>
+        <v>-1229600</v>
       </c>
       <c r="I89" s="3">
-        <v>-1093100</v>
+        <v>-1115400</v>
       </c>
       <c r="J89" s="3">
-        <v>-632000</v>
+        <v>-644900</v>
       </c>
       <c r="K89" s="3">
         <v>-304000</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1981300</v>
+        <v>-2021800</v>
       </c>
       <c r="E91" s="3">
-        <v>-963400</v>
+        <v>-983000</v>
       </c>
       <c r="F91" s="3">
-        <v>-563500</v>
+        <v>-575000</v>
       </c>
       <c r="G91" s="3">
-        <v>-155800</v>
+        <v>-159000</v>
       </c>
       <c r="H91" s="3">
-        <v>-235800</v>
+        <v>-240600</v>
       </c>
       <c r="I91" s="3">
-        <v>-365300</v>
+        <v>-372700</v>
       </c>
       <c r="J91" s="3">
-        <v>-153900</v>
+        <v>-157000</v>
       </c>
       <c r="K91" s="3">
         <v>-90400</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1503900</v>
+        <v>-1534600</v>
       </c>
       <c r="E94" s="3">
-        <v>1434800</v>
+        <v>1464100</v>
       </c>
       <c r="F94" s="3">
-        <v>-5493900</v>
+        <v>-5606000</v>
       </c>
       <c r="G94" s="3">
-        <v>-700600</v>
+        <v>-714900</v>
       </c>
       <c r="H94" s="3">
-        <v>467300</v>
+        <v>476800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1097100</v>
+        <v>-1119500</v>
       </c>
       <c r="J94" s="3">
-        <v>-164400</v>
+        <v>-167800</v>
       </c>
       <c r="K94" s="3">
         <v>16300</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>3821900</v>
+        <v>3899900</v>
       </c>
       <c r="E100" s="3">
-        <v>-223300</v>
+        <v>-227900</v>
       </c>
       <c r="F100" s="3">
-        <v>2504700</v>
+        <v>2555800</v>
       </c>
       <c r="G100" s="3">
-        <v>5713900</v>
+        <v>5830600</v>
       </c>
       <c r="H100" s="3">
-        <v>427600</v>
+        <v>436300</v>
       </c>
       <c r="I100" s="3">
-        <v>1603100</v>
+        <v>1635800</v>
       </c>
       <c r="J100" s="3">
-        <v>1777800</v>
+        <v>1814000</v>
       </c>
       <c r="K100" s="3">
         <v>316600</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>9700</v>
+        <v>9900</v>
       </c>
       <c r="E101" s="3">
-        <v>-16800</v>
+        <v>-17200</v>
       </c>
       <c r="F101" s="3">
-        <v>-69200</v>
+        <v>-70600</v>
       </c>
       <c r="G101" s="3">
-        <v>-94200</v>
+        <v>-96200</v>
       </c>
       <c r="H101" s="3">
         <v>1400</v>
       </c>
       <c r="I101" s="3">
-        <v>-7900</v>
+        <v>-8000</v>
       </c>
       <c r="J101" s="3">
-        <v>-23200</v>
+        <v>-23700</v>
       </c>
       <c r="K101" s="3">
         <v>5600</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2136800</v>
+        <v>2180400</v>
       </c>
       <c r="E102" s="3">
-        <v>660500</v>
+        <v>674000</v>
       </c>
       <c r="F102" s="3">
-        <v>-2786800</v>
+        <v>-2843600</v>
       </c>
       <c r="G102" s="3">
-        <v>5188600</v>
+        <v>5294500</v>
       </c>
       <c r="H102" s="3">
-        <v>-308700</v>
+        <v>-315000</v>
       </c>
       <c r="I102" s="3">
-        <v>-595000</v>
+        <v>-607100</v>
       </c>
       <c r="J102" s="3">
-        <v>958000</v>
+        <v>977600</v>
       </c>
       <c r="K102" s="3">
         <v>34500</v>

--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>NIO</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -728,22 +728,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>7841000</v>
+        <v>7843600</v>
       </c>
       <c r="E8" s="3">
-        <v>6945900</v>
+        <v>7143300</v>
       </c>
       <c r="F8" s="3">
-        <v>5094500</v>
+        <v>5688400</v>
       </c>
       <c r="G8" s="3">
-        <v>2292000</v>
+        <v>2490300</v>
       </c>
       <c r="H8" s="3">
-        <v>1103200</v>
+        <v>1123800</v>
       </c>
       <c r="I8" s="3">
-        <v>698000</v>
+        <v>719900</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -773,22 +773,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>7410800</v>
+        <v>7413200</v>
       </c>
       <c r="E9" s="3">
-        <v>6220700</v>
+        <v>6397500</v>
       </c>
       <c r="F9" s="3">
-        <v>4132800</v>
+        <v>4614600</v>
       </c>
       <c r="G9" s="3">
-        <v>2027900</v>
+        <v>2203300</v>
       </c>
       <c r="H9" s="3">
-        <v>1272200</v>
+        <v>1296000</v>
       </c>
       <c r="I9" s="3">
-        <v>734100</v>
+        <v>757100</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -818,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>430200</v>
+        <v>430400</v>
       </c>
       <c r="E10" s="3">
-        <v>725200</v>
+        <v>745800</v>
       </c>
       <c r="F10" s="3">
-        <v>961700</v>
+        <v>1073800</v>
       </c>
       <c r="G10" s="3">
-        <v>264100</v>
+        <v>287000</v>
       </c>
       <c r="H10" s="3">
-        <v>-169000</v>
+        <v>-172200</v>
       </c>
       <c r="I10" s="3">
-        <v>-36100</v>
+        <v>-37200</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -882,25 +882,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1791900</v>
+        <v>1855600</v>
       </c>
       <c r="E12" s="3">
-        <v>1480700</v>
+        <v>1543100</v>
       </c>
       <c r="F12" s="3">
-        <v>617100</v>
+        <v>714400</v>
       </c>
       <c r="G12" s="3">
-        <v>314700</v>
+        <v>373200</v>
       </c>
       <c r="H12" s="3">
-        <v>598000</v>
+        <v>627800</v>
       </c>
       <c r="I12" s="3">
-        <v>549000</v>
+        <v>576500</v>
       </c>
       <c r="J12" s="3">
-        <v>361500</v>
+        <v>398100</v>
       </c>
       <c r="K12" s="3">
         <v>201300</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-24000</v>
+        <v>18800</v>
       </c>
       <c r="E14" s="3">
-        <v>-19500</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>20400</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1036800</v>
+      </c>
+      <c r="G14" s="3">
+        <v>47700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>18200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1996400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>396000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>196400</v>
+        <v>476400</v>
       </c>
       <c r="E15" s="3">
-        <v>115200</v>
+        <v>413500</v>
       </c>
       <c r="F15" s="3">
-        <v>77800</v>
+        <v>268900</v>
       </c>
       <c r="G15" s="3">
-        <v>81900</v>
+        <v>160300</v>
       </c>
       <c r="H15" s="3">
-        <v>90900</v>
+        <v>143500</v>
       </c>
       <c r="I15" s="3">
-        <v>49800</v>
+        <v>69000</v>
       </c>
       <c r="J15" s="3">
-        <v>23700</v>
+        <v>25800</v>
       </c>
       <c r="K15" s="3">
         <v>6400</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11011000</v>
+        <v>11038500</v>
       </c>
       <c r="E17" s="3">
-        <v>9131400</v>
+        <v>9411000</v>
       </c>
       <c r="F17" s="3">
-        <v>5728400</v>
+        <v>6396200</v>
       </c>
       <c r="G17" s="3">
-        <v>2941600</v>
+        <v>3196000</v>
       </c>
       <c r="H17" s="3">
-        <v>2665100</v>
+        <v>2715000</v>
       </c>
       <c r="I17" s="3">
-        <v>2050800</v>
+        <v>2115100</v>
       </c>
       <c r="J17" s="3">
-        <v>698400</v>
+        <v>761300</v>
       </c>
       <c r="K17" s="3">
         <v>359400</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3169900</v>
+        <v>-3195000</v>
       </c>
       <c r="E18" s="3">
-        <v>-2185500</v>
+        <v>-2267700</v>
       </c>
       <c r="F18" s="3">
-        <v>-633900</v>
+        <v>-707800</v>
       </c>
       <c r="G18" s="3">
-        <v>-649600</v>
+        <v>-705800</v>
       </c>
       <c r="H18" s="3">
-        <v>-1561900</v>
+        <v>-1591200</v>
       </c>
       <c r="I18" s="3">
-        <v>-1352800</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-1395200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-761300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>342500</v>
+        <v>-31000</v>
       </c>
       <c r="E20" s="3">
-        <v>204900</v>
+        <v>-13700</v>
       </c>
       <c r="F20" s="3">
-        <v>163400</v>
+        <v>-38900</v>
       </c>
       <c r="G20" s="3">
-        <v>-37200</v>
+        <v>66000</v>
       </c>
       <c r="H20" s="3">
-        <v>22800</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>14400</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>4500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>9800</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2352800</v>
+        <v>-2687600</v>
       </c>
       <c r="E21" s="3">
-        <v>-1579800</v>
+        <v>-1840400</v>
       </c>
       <c r="F21" s="3">
-        <v>-230500</v>
+        <v>-400000</v>
       </c>
       <c r="G21" s="3">
-        <v>-539800</v>
+        <v>-611500</v>
       </c>
       <c r="H21" s="3">
-        <v>-1398800</v>
+        <v>-1447500</v>
       </c>
       <c r="I21" s="3">
-        <v>-1271700</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-1330700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-745400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1280,22 +1280,22 @@
         <v>56900</v>
       </c>
       <c r="E22" s="3">
-        <v>47000</v>
+        <v>48300</v>
       </c>
       <c r="F22" s="3">
-        <v>89900</v>
+        <v>100300</v>
       </c>
       <c r="G22" s="3">
-        <v>60100</v>
+        <v>65300</v>
       </c>
       <c r="H22" s="3">
-        <v>52200</v>
+        <v>53200</v>
       </c>
       <c r="I22" s="3">
-        <v>17400</v>
+        <v>18000</v>
       </c>
       <c r="J22" s="3">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2884300</v>
+        <v>-2928000</v>
       </c>
       <c r="E23" s="3">
-        <v>-2027600</v>
+        <v>-2125700</v>
       </c>
       <c r="F23" s="3">
-        <v>-560400</v>
+        <v>-1662500</v>
       </c>
       <c r="G23" s="3">
-        <v>-746900</v>
+        <v>-859200</v>
       </c>
       <c r="H23" s="3">
-        <v>-1591300</v>
+        <v>-1639300</v>
       </c>
       <c r="I23" s="3">
-        <v>-1355800</v>
+        <v>-3394700</v>
       </c>
       <c r="J23" s="3">
-        <v>-706800</v>
+        <v>-1166500</v>
       </c>
       <c r="K23" s="3">
         <v>-354700</v>
@@ -1370,22 +1370,22 @@
         <v>36800</v>
       </c>
       <c r="E24" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="F24" s="3">
-        <v>6000</v>
+        <v>6700</v>
       </c>
       <c r="G24" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H24" s="3">
         <v>1100</v>
       </c>
       <c r="I24" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="J24" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="K24" s="3">
         <v>600</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2921100</v>
+        <v>-2964800</v>
       </c>
       <c r="E26" s="3">
-        <v>-2035300</v>
+        <v>-2133700</v>
       </c>
       <c r="F26" s="3">
-        <v>-566300</v>
+        <v>-1669200</v>
       </c>
       <c r="G26" s="3">
-        <v>-747800</v>
+        <v>-860200</v>
       </c>
       <c r="H26" s="3">
-        <v>-1592500</v>
+        <v>-1640400</v>
       </c>
       <c r="I26" s="3">
-        <v>-1358900</v>
+        <v>-3397900</v>
       </c>
       <c r="J26" s="3">
-        <v>-707900</v>
+        <v>-1167700</v>
       </c>
       <c r="K26" s="3">
         <v>-355300</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2981300</v>
+        <v>-2982300</v>
       </c>
       <c r="E27" s="3">
-        <v>-2052600</v>
+        <v>-2110900</v>
       </c>
       <c r="F27" s="3">
-        <v>-1490500</v>
+        <v>-1664300</v>
       </c>
       <c r="G27" s="3">
-        <v>-791000</v>
+        <v>-859400</v>
       </c>
       <c r="H27" s="3">
-        <v>-1609000</v>
+        <v>-1639100</v>
       </c>
       <c r="I27" s="3">
-        <v>-3288800</v>
+        <v>-3391800</v>
       </c>
       <c r="J27" s="3">
-        <v>-1066000</v>
+        <v>-1162100</v>
       </c>
       <c r="K27" s="3">
         <v>-485700</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-342500</v>
+        <v>31000</v>
       </c>
       <c r="E32" s="3">
-        <v>-204900</v>
+        <v>13700</v>
       </c>
       <c r="F32" s="3">
-        <v>-163400</v>
+        <v>38900</v>
       </c>
       <c r="G32" s="3">
-        <v>37200</v>
+        <v>-66000</v>
       </c>
       <c r="H32" s="3">
-        <v>-22800</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-4500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-9800</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2981300</v>
+        <v>-2982300</v>
       </c>
       <c r="E33" s="3">
-        <v>-2052600</v>
+        <v>-2110900</v>
       </c>
       <c r="F33" s="3">
-        <v>-1490500</v>
+        <v>-1664200</v>
       </c>
       <c r="G33" s="3">
-        <v>-791000</v>
+        <v>-859400</v>
       </c>
       <c r="H33" s="3">
-        <v>-1609000</v>
+        <v>-1639100</v>
       </c>
       <c r="I33" s="3">
-        <v>-3288800</v>
+        <v>-3391800</v>
       </c>
       <c r="J33" s="3">
-        <v>-1066000</v>
+        <v>-1162100</v>
       </c>
       <c r="K33" s="3">
         <v>-485700</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2981300</v>
+        <v>-2982300</v>
       </c>
       <c r="E35" s="3">
-        <v>-2052600</v>
+        <v>-2110900</v>
       </c>
       <c r="F35" s="3">
-        <v>-1490500</v>
+        <v>-1664200</v>
       </c>
       <c r="G35" s="3">
-        <v>-791000</v>
+        <v>-859400</v>
       </c>
       <c r="H35" s="3">
-        <v>-1609000</v>
+        <v>-1639100</v>
       </c>
       <c r="I35" s="3">
-        <v>-3288800</v>
+        <v>-3391800</v>
       </c>
       <c r="J35" s="3">
-        <v>-1066000</v>
+        <v>-1162100</v>
       </c>
       <c r="K35" s="3">
         <v>-485700</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4643200</v>
+        <v>4644700</v>
       </c>
       <c r="E41" s="3">
-        <v>2803800</v>
+        <v>2883400</v>
       </c>
       <c r="F41" s="3">
-        <v>2161700</v>
+        <v>2413800</v>
       </c>
       <c r="G41" s="3">
-        <v>5417200</v>
+        <v>5885700</v>
       </c>
       <c r="H41" s="3">
-        <v>121600</v>
+        <v>123900</v>
       </c>
       <c r="I41" s="3">
-        <v>441800</v>
+        <v>455700</v>
       </c>
       <c r="J41" s="3">
-        <v>1058200</v>
+        <v>1153600</v>
       </c>
       <c r="K41" s="3">
         <v>80300</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2369900</v>
+        <v>2404600</v>
       </c>
       <c r="E42" s="3">
-        <v>2702700</v>
+        <v>2830200</v>
       </c>
       <c r="F42" s="3">
-        <v>5224400</v>
+        <v>5846700</v>
       </c>
       <c r="G42" s="3">
-        <v>557000</v>
+        <v>612200</v>
       </c>
       <c r="H42" s="3">
-        <v>15600</v>
+        <v>26500</v>
       </c>
       <c r="I42" s="3">
-        <v>726700</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>752900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1900</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1240900</v>
+        <v>948800</v>
       </c>
       <c r="E43" s="3">
-        <v>1044800</v>
+        <v>1025700</v>
       </c>
       <c r="F43" s="3">
-        <v>791100</v>
+        <v>756100</v>
       </c>
       <c r="G43" s="3">
-        <v>337800</v>
+        <v>251500</v>
       </c>
       <c r="H43" s="3">
-        <v>397600</v>
+        <v>228100</v>
       </c>
       <c r="I43" s="3">
-        <v>282300</v>
+        <v>142600</v>
       </c>
       <c r="J43" s="3">
-        <v>71300</v>
+        <v>4200</v>
       </c>
       <c r="K43" s="3">
         <v>25300</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>744100</v>
+        <v>744300</v>
       </c>
       <c r="E44" s="3">
-        <v>1154800</v>
+        <v>1187600</v>
       </c>
       <c r="F44" s="3">
-        <v>289900</v>
+        <v>323700</v>
       </c>
       <c r="G44" s="3">
-        <v>152500</v>
+        <v>165700</v>
       </c>
       <c r="H44" s="3">
-        <v>125400</v>
+        <v>127800</v>
       </c>
       <c r="I44" s="3">
-        <v>206600</v>
+        <v>213000</v>
       </c>
       <c r="J44" s="3">
-        <v>12600</v>
+        <v>13700</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>924100</v>
+        <v>401400</v>
       </c>
       <c r="E45" s="3">
-        <v>632900</v>
+        <v>191500</v>
       </c>
       <c r="F45" s="3">
-        <v>505000</v>
+        <v>206500</v>
       </c>
       <c r="G45" s="3">
-        <v>49800</v>
+        <v>150600</v>
       </c>
       <c r="H45" s="3">
-        <v>34500</v>
+        <v>189700</v>
       </c>
       <c r="I45" s="3">
-        <v>58300</v>
+        <v>197000</v>
       </c>
       <c r="J45" s="3">
-        <v>29400</v>
+        <v>102000</v>
       </c>
       <c r="K45" s="3">
         <v>15300</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9922200</v>
+        <v>9925400</v>
       </c>
       <c r="E46" s="3">
-        <v>8338900</v>
+        <v>8575900</v>
       </c>
       <c r="F46" s="3">
-        <v>8972200</v>
+        <v>10018200</v>
       </c>
       <c r="G46" s="3">
-        <v>6514200</v>
+        <v>7077600</v>
       </c>
       <c r="H46" s="3">
-        <v>694800</v>
+        <v>707800</v>
       </c>
       <c r="I46" s="3">
-        <v>1715700</v>
+        <v>1769400</v>
       </c>
       <c r="J46" s="3">
-        <v>1171500</v>
+        <v>1277100</v>
       </c>
       <c r="K46" s="3">
         <v>120800</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1132500</v>
+        <v>773800</v>
       </c>
       <c r="E47" s="3">
-        <v>1734900</v>
+        <v>921600</v>
       </c>
       <c r="F47" s="3">
-        <v>1066500</v>
+        <v>481600</v>
       </c>
       <c r="G47" s="3">
-        <v>224000</v>
+        <v>46000</v>
       </c>
       <c r="H47" s="3">
-        <v>109000</v>
+        <v>16600</v>
       </c>
       <c r="I47" s="3">
-        <v>103000</v>
+        <v>21600</v>
       </c>
       <c r="J47" s="3">
-        <v>13700</v>
+        <v>7200</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5118600</v>
+        <v>5120200</v>
       </c>
       <c r="E48" s="3">
-        <v>3254100</v>
+        <v>3346600</v>
       </c>
       <c r="F48" s="3">
-        <v>1473800</v>
+        <v>1645600</v>
       </c>
       <c r="G48" s="3">
-        <v>908300</v>
+        <v>986800</v>
       </c>
       <c r="H48" s="3">
-        <v>1083500</v>
+        <v>1103800</v>
       </c>
       <c r="I48" s="3">
-        <v>684200</v>
+        <v>705600</v>
       </c>
       <c r="J48" s="3">
-        <v>269400</v>
+        <v>293700</v>
       </c>
       <c r="K48" s="3">
         <v>115000</v>
@@ -2358,22 +2358,22 @@
         <v>33400</v>
       </c>
       <c r="E49" s="3">
-        <v>30000</v>
+        <v>30800</v>
       </c>
       <c r="F49" s="3">
-        <v>28100</v>
+        <v>31300</v>
       </c>
       <c r="G49" s="3">
-        <v>28800</v>
+        <v>31300</v>
       </c>
       <c r="H49" s="3">
-        <v>29700</v>
+        <v>30200</v>
       </c>
       <c r="I49" s="3">
-        <v>30600</v>
+        <v>31600</v>
       </c>
       <c r="J49" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K49" s="3">
         <v>900</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>342000</v>
+        <v>342100</v>
       </c>
       <c r="E52" s="3">
-        <v>213300</v>
+        <v>397300</v>
       </c>
       <c r="F52" s="3">
-        <v>144400</v>
+        <v>465700</v>
       </c>
       <c r="G52" s="3">
-        <v>28100</v>
+        <v>130300</v>
       </c>
       <c r="H52" s="3">
-        <v>138800</v>
+        <v>141400</v>
       </c>
       <c r="I52" s="3">
-        <v>122900</v>
+        <v>127900</v>
       </c>
       <c r="J52" s="3">
-        <v>20500</v>
+        <v>22400</v>
       </c>
       <c r="K52" s="3">
         <v>7700</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16548700</v>
+        <v>16554100</v>
       </c>
       <c r="E54" s="3">
-        <v>13571300</v>
+        <v>13957000</v>
       </c>
       <c r="F54" s="3">
-        <v>11684900</v>
+        <v>13047200</v>
       </c>
       <c r="G54" s="3">
-        <v>7703400</v>
+        <v>8369600</v>
       </c>
       <c r="H54" s="3">
-        <v>2055800</v>
+        <v>2094200</v>
       </c>
       <c r="I54" s="3">
-        <v>2656400</v>
+        <v>2739700</v>
       </c>
       <c r="J54" s="3">
-        <v>1475800</v>
+        <v>1608800</v>
       </c>
       <c r="K54" s="3">
         <v>244500</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4823200</v>
+        <v>4264800</v>
       </c>
       <c r="E57" s="3">
-        <v>4144300</v>
+        <v>3700500</v>
       </c>
       <c r="F57" s="3">
-        <v>1987500</v>
+        <v>2070900</v>
       </c>
       <c r="G57" s="3">
-        <v>998700</v>
+        <v>1027200</v>
       </c>
       <c r="H57" s="3">
-        <v>596800</v>
+        <v>477600</v>
       </c>
       <c r="I57" s="3">
-        <v>549400</v>
+        <v>447900</v>
       </c>
       <c r="J57" s="3">
-        <v>90900</v>
+        <v>39000</v>
       </c>
       <c r="K57" s="3">
         <v>26300</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1388200</v>
+        <v>1634500</v>
       </c>
       <c r="E58" s="3">
-        <v>748300</v>
+        <v>918300</v>
       </c>
       <c r="F58" s="3">
-        <v>1032800</v>
+        <v>1270400</v>
       </c>
       <c r="G58" s="3">
-        <v>276900</v>
+        <v>384600</v>
       </c>
       <c r="H58" s="3">
-        <v>176000</v>
+        <v>266700</v>
       </c>
       <c r="I58" s="3">
-        <v>291700</v>
+        <v>300800</v>
       </c>
       <c r="J58" s="3">
-        <v>11800</v>
+        <v>12900</v>
       </c>
       <c r="K58" s="3">
         <v>2700</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1937000</v>
+        <v>1270600</v>
       </c>
       <c r="E59" s="3">
-        <v>1571600</v>
+        <v>1141100</v>
       </c>
       <c r="F59" s="3">
-        <v>1096100</v>
+        <v>738200</v>
       </c>
       <c r="G59" s="3">
-        <v>694800</v>
+        <v>440100</v>
       </c>
       <c r="H59" s="3">
-        <v>566300</v>
+        <v>344800</v>
       </c>
       <c r="I59" s="3">
-        <v>370400</v>
+        <v>264300</v>
       </c>
       <c r="J59" s="3">
-        <v>125500</v>
+        <v>90700</v>
       </c>
       <c r="K59" s="3">
         <v>71300</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8148400</v>
+        <v>8151000</v>
       </c>
       <c r="E60" s="3">
-        <v>6464200</v>
+        <v>6647900</v>
       </c>
       <c r="F60" s="3">
-        <v>4116400</v>
+        <v>4596300</v>
       </c>
       <c r="G60" s="3">
-        <v>1970400</v>
+        <v>2140800</v>
       </c>
       <c r="H60" s="3">
-        <v>1339100</v>
+        <v>1364200</v>
       </c>
       <c r="I60" s="3">
-        <v>1211500</v>
+        <v>1249500</v>
       </c>
       <c r="J60" s="3">
-        <v>228200</v>
+        <v>248700</v>
       </c>
       <c r="K60" s="3">
         <v>100300</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1841900</v>
+        <v>3262600</v>
       </c>
       <c r="E61" s="3">
-        <v>1536700</v>
+        <v>2525300</v>
       </c>
       <c r="F61" s="3">
-        <v>1377500</v>
+        <v>1902800</v>
       </c>
       <c r="G61" s="3">
-        <v>844900</v>
+        <v>1073500</v>
       </c>
       <c r="H61" s="3">
-        <v>1021200</v>
+        <v>1269900</v>
       </c>
       <c r="I61" s="3">
-        <v>164700</v>
+        <v>169800</v>
       </c>
       <c r="J61" s="3">
-        <v>90600</v>
+        <v>98700</v>
       </c>
       <c r="K61" s="3">
         <v>5200</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2386000</v>
+        <v>460700</v>
       </c>
       <c r="E62" s="3">
-        <v>1672700</v>
+        <v>367100</v>
       </c>
       <c r="F62" s="3">
-        <v>824900</v>
+        <v>274600</v>
       </c>
       <c r="G62" s="3">
-        <v>396200</v>
+        <v>121100</v>
       </c>
       <c r="H62" s="3">
-        <v>375200</v>
+        <v>61200</v>
       </c>
       <c r="I62" s="3">
-        <v>131200</v>
+        <v>56000</v>
       </c>
       <c r="J62" s="3">
-        <v>19900</v>
+        <v>17000</v>
       </c>
       <c r="K62" s="3">
         <v>8500</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12947200</v>
+        <v>12380300</v>
       </c>
       <c r="E66" s="3">
-        <v>10206400</v>
+        <v>9948600</v>
       </c>
       <c r="F66" s="3">
-        <v>6791500</v>
+        <v>7055400</v>
       </c>
       <c r="G66" s="3">
-        <v>3873200</v>
+        <v>3489200</v>
       </c>
       <c r="H66" s="3">
-        <v>2943900</v>
+        <v>2786700</v>
       </c>
       <c r="I66" s="3">
-        <v>1692500</v>
+        <v>1554600</v>
       </c>
       <c r="J66" s="3">
-        <v>340200</v>
+        <v>369200</v>
       </c>
       <c r="K66" s="3">
         <v>112400</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>2771400</v>
+        <v>3021200</v>
       </c>
       <c r="K70" s="3">
         <v>671300</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-12795100</v>
+        <v>-12799200</v>
       </c>
       <c r="E72" s="3">
-        <v>-9856500</v>
+        <v>-10136600</v>
       </c>
       <c r="F72" s="3">
-        <v>-7843300</v>
+        <v>-8757700</v>
       </c>
       <c r="G72" s="3">
-        <v>-7281400</v>
+        <v>-7911100</v>
       </c>
       <c r="H72" s="3">
-        <v>-6531100</v>
+        <v>-6653300</v>
       </c>
       <c r="I72" s="3">
-        <v>-4939900</v>
+        <v>-5094700</v>
       </c>
       <c r="J72" s="3">
-        <v>-1651200</v>
+        <v>-1800000</v>
       </c>
       <c r="K72" s="3">
         <v>-562900</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3601500</v>
+        <v>3602700</v>
       </c>
       <c r="E76" s="3">
-        <v>3364900</v>
+        <v>3460600</v>
       </c>
       <c r="F76" s="3">
-        <v>4893400</v>
+        <v>5463900</v>
       </c>
       <c r="G76" s="3">
-        <v>3830300</v>
+        <v>4161500</v>
       </c>
       <c r="H76" s="3">
-        <v>-888100</v>
+        <v>-904800</v>
       </c>
       <c r="I76" s="3">
-        <v>963900</v>
+        <v>994100</v>
       </c>
       <c r="J76" s="3">
-        <v>-1635800</v>
+        <v>-1783300</v>
       </c>
       <c r="K76" s="3">
         <v>-539200</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2981300</v>
+        <v>-2982300</v>
       </c>
       <c r="E81" s="3">
-        <v>-2052600</v>
+        <v>-2110900</v>
       </c>
       <c r="F81" s="3">
-        <v>-1490500</v>
+        <v>-1664200</v>
       </c>
       <c r="G81" s="3">
-        <v>-791000</v>
+        <v>-859400</v>
       </c>
       <c r="H81" s="3">
-        <v>-1609000</v>
+        <v>-1639100</v>
       </c>
       <c r="I81" s="3">
-        <v>-3288800</v>
+        <v>-3391800</v>
       </c>
       <c r="J81" s="3">
-        <v>-1066000</v>
+        <v>-1162100</v>
       </c>
       <c r="K81" s="3">
         <v>-485700</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>476200</v>
+        <v>691300</v>
       </c>
       <c r="E83" s="3">
-        <v>402100</v>
+        <v>578300</v>
       </c>
       <c r="F83" s="3">
-        <v>240800</v>
+        <v>369500</v>
       </c>
       <c r="G83" s="3">
-        <v>147500</v>
+        <v>235900</v>
       </c>
       <c r="H83" s="3">
-        <v>140800</v>
+        <v>217600</v>
       </c>
       <c r="I83" s="3">
-        <v>66900</v>
+        <v>68300</v>
       </c>
       <c r="J83" s="3">
-        <v>23700</v>
+        <v>25500</v>
       </c>
       <c r="K83" s="3">
         <v>6400</v>
@@ -3969,22 +3969,22 @@
         <v>-194800</v>
       </c>
       <c r="E89" s="3">
-        <v>-545000</v>
+        <v>-560500</v>
       </c>
       <c r="F89" s="3">
-        <v>277200</v>
+        <v>309500</v>
       </c>
       <c r="G89" s="3">
-        <v>275000</v>
+        <v>298800</v>
       </c>
       <c r="H89" s="3">
-        <v>-1229600</v>
+        <v>-1252600</v>
       </c>
       <c r="I89" s="3">
-        <v>-1115400</v>
+        <v>-1150400</v>
       </c>
       <c r="J89" s="3">
-        <v>-644900</v>
+        <v>-703100</v>
       </c>
       <c r="K89" s="3">
         <v>-304000</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2021800</v>
+        <v>-2022400</v>
       </c>
       <c r="E91" s="3">
-        <v>-983000</v>
+        <v>-1011000</v>
       </c>
       <c r="F91" s="3">
-        <v>-575000</v>
+        <v>-642100</v>
       </c>
       <c r="G91" s="3">
-        <v>-159000</v>
+        <v>-172700</v>
       </c>
       <c r="H91" s="3">
-        <v>-240600</v>
+        <v>-245100</v>
       </c>
       <c r="I91" s="3">
-        <v>-372700</v>
+        <v>-384400</v>
       </c>
       <c r="J91" s="3">
-        <v>-157000</v>
+        <v>-171200</v>
       </c>
       <c r="K91" s="3">
         <v>-90400</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1534600</v>
+        <v>-1535100</v>
       </c>
       <c r="E94" s="3">
-        <v>1464100</v>
+        <v>1505700</v>
       </c>
       <c r="F94" s="3">
-        <v>-5606000</v>
+        <v>-6259600</v>
       </c>
       <c r="G94" s="3">
-        <v>-714900</v>
+        <v>-776700</v>
       </c>
       <c r="H94" s="3">
-        <v>476800</v>
+        <v>485700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1119500</v>
+        <v>-1154600</v>
       </c>
       <c r="J94" s="3">
-        <v>-167800</v>
+        <v>-182900</v>
       </c>
       <c r="K94" s="3">
         <v>16300</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>3899900</v>
+        <v>3901200</v>
       </c>
       <c r="E100" s="3">
-        <v>-227900</v>
+        <v>-234400</v>
       </c>
       <c r="F100" s="3">
-        <v>2555800</v>
+        <v>2853800</v>
       </c>
       <c r="G100" s="3">
-        <v>5830600</v>
+        <v>6334800</v>
       </c>
       <c r="H100" s="3">
-        <v>436300</v>
+        <v>444500</v>
       </c>
       <c r="I100" s="3">
-        <v>1635800</v>
+        <v>1687100</v>
       </c>
       <c r="J100" s="3">
-        <v>1814000</v>
+        <v>1977600</v>
       </c>
       <c r="K100" s="3">
         <v>316600</v>
@@ -4457,22 +4457,22 @@
         <v>9900</v>
       </c>
       <c r="E101" s="3">
-        <v>-17200</v>
+        <v>-17700</v>
       </c>
       <c r="F101" s="3">
-        <v>-70600</v>
+        <v>-78900</v>
       </c>
       <c r="G101" s="3">
-        <v>-96200</v>
+        <v>-104500</v>
       </c>
       <c r="H101" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="I101" s="3">
-        <v>-8000</v>
+        <v>-8300</v>
       </c>
       <c r="J101" s="3">
-        <v>-23700</v>
+        <v>-25800</v>
       </c>
       <c r="K101" s="3">
         <v>5600</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2180400</v>
+        <v>2181100</v>
       </c>
       <c r="E102" s="3">
-        <v>674000</v>
+        <v>693100</v>
       </c>
       <c r="F102" s="3">
-        <v>-2843600</v>
+        <v>-3175200</v>
       </c>
       <c r="G102" s="3">
-        <v>5294500</v>
+        <v>5752400</v>
       </c>
       <c r="H102" s="3">
-        <v>-315000</v>
+        <v>-320900</v>
       </c>
       <c r="I102" s="3">
-        <v>-607100</v>
+        <v>-626100</v>
       </c>
       <c r="J102" s="3">
-        <v>977600</v>
+        <v>1065700</v>
       </c>
       <c r="K102" s="3">
         <v>34500</v>

--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>NIO</t>
   </si>
@@ -656,59 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,33 +722,36 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9005400</v>
+      </c>
+      <c r="E8" s="3">
         <v>7843600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7143300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5688400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2490300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1123800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>719900</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -763,36 +767,39 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8115900</v>
+      </c>
+      <c r="E9" s="3">
         <v>7413200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6397500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4614600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2203300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1296000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>757100</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,33 +818,36 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>889500</v>
+      </c>
+      <c r="E10" s="3">
         <v>430400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>745800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1073800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>287000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-172200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-37200</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +866,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,38 +889,39 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1786200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1855600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1543100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>714400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>373200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>627800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>576500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>398100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>201300</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,9 +934,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,38 +982,41 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E14" s="3">
         <v>18800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>20400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1036800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>47700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1996400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>396000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1010,39 +1030,42 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>462800</v>
+      </c>
+      <c r="E15" s="3">
         <v>476400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>413500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>268900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>160300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>143500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>69000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6400</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,9 +1078,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,38 +1098,39 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12002300</v>
+      </c>
+      <c r="E17" s="3">
         <v>11038500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9411000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6396200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3196000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2715000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2115100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>761300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>359400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,36 +1143,39 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2996800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3195000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2267700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-707800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-705800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1591200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1395200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-761300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,9 +1191,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,35 +1214,36 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-38900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>66000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,36 +1259,39 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2616400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2687600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1840400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-611500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1447500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1330700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-745400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,38 +1307,41 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E22" s="3">
         <v>56900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>48300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>65300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>53200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2800</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1315,39 +1355,42 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3119800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2928000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2125700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1662500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-859200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1639300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3394700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1166500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-354700</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,39 +1403,42 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>36800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,9 +1451,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,39 +1499,42 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3116700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2964800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2133700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1669200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-860200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1640400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3397900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1167700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-355300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,39 +1547,42 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3104200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2982300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2110900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1664300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-859400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1639100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3391800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1162100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-485700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,9 +1595,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1691,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,36 +1787,39 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E32" s="3">
         <v>31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>38900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-66000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,39 +1835,42 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3104200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2982300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2110900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1664200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-859400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1639100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3391800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1162100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-485700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,9 +1883,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,39 +1931,42 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3104200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2982300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2110900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1664200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-859400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1639100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3391800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1162100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-485700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1900,44 +1979,47 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1950,9 +2032,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,38 +2075,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2648100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4644700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2883400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2413800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5885700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>123900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>455700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1153600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,36 +2120,39 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1936900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2404600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2830200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5846700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>612200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>752900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1900</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2075,42 +2165,45 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1284900</v>
+      </c>
+      <c r="E43" s="3">
         <v>948800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1025700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>756100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>251500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>228100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>142600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,38 +2216,41 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>971000</v>
+      </c>
+      <c r="E44" s="3">
         <v>744300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1187600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>323700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>165700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>127800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>213000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13700</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2168,39 +2264,42 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>497700</v>
+      </c>
+      <c r="E45" s="3">
         <v>401400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>191500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>206500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>150600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>189700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>197000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>102000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2213,39 +2312,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8478600</v>
+      </c>
+      <c r="E46" s="3">
         <v>9925400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8575900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10018200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7077600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>707800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1769400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1277100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>120800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2258,38 +2360,41 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>428300</v>
+      </c>
+      <c r="E47" s="3">
         <v>773800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>921600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>481600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>21600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7200</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
+      <c r="L47" s="3">
+        <v>0</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
@@ -2303,39 +2408,42 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5300700</v>
+      </c>
+      <c r="E48" s="3">
         <v>5120200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3346600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1645600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>986800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1103800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>705600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>293700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>115000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2348,39 +2456,42 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E49" s="3">
         <v>33400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30800</v>
-      </c>
-      <c r="F49" s="3">
-        <v>31300</v>
       </c>
       <c r="G49" s="3">
         <v>31300</v>
       </c>
       <c r="H49" s="3">
+        <v>31300</v>
+      </c>
+      <c r="I49" s="3">
         <v>30200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>31600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,9 +2504,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,39 +2600,42 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>502900</v>
+      </c>
+      <c r="E52" s="3">
         <v>342100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>397300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>465700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>130300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>141400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>127900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,9 +2648,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,39 +2696,42 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14742200</v>
+      </c>
+      <c r="E54" s="3">
         <v>16554100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13957000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13047200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8369600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2094200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2739700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1608800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>244500</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,9 +2744,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,38 +2787,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4711200</v>
+      </c>
+      <c r="E57" s="3">
         <v>4264800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2070900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1027200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>477600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>447900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,39 +2832,42 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1517100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1634500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>918300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1270400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>384600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>266700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,39 +2880,42 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1270600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1141100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>738200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>440100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>344800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>264300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>90700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,39 +2928,42 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8536800</v>
+      </c>
+      <c r="E60" s="3">
         <v>8151000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6647900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4596300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2140800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1364200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1249500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>248700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,39 +2976,42 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3110200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3262600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2525300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1902800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1073500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1269900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>169800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>98700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2881,39 +3024,42 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1227300</v>
+      </c>
+      <c r="E62" s="3">
         <v>460700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>367100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>274600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>121100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>56000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,9 +3072,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,39 +3216,42 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12891700</v>
+      </c>
+      <c r="E66" s="3">
         <v>12380300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9948600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7055400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3489200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2786700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1554600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>369200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,9 +3264,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3240,14 +3408,14 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>3021200</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>671300</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3260,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,39 +3476,42 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12799200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10136600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8757700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7911100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6653300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5094700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1800000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-562900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,9 +3524,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,39 +3668,42 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>817500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3602700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3460600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5463900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4161500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-904800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>994100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1783300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-539200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,9 +3716,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,44 +3764,47 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3625,39 +3817,42 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3104200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2982300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2110900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1664200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-859400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1639100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3391800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1162100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-485700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,9 +3865,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,38 +3888,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>691300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>578300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>369500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>235900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>217600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>68300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6400</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,9 +3933,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,39 +4173,42 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-194800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-560500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>309500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>298800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1252600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1150400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-703100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-304000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,9 +4221,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,38 +4244,39 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2022400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1011000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-642100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-172700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-245100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-384400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-171200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-90400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,9 +4289,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,39 +4385,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1535100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1505700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6259600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-776700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>485700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1154600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-182900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>16300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,9 +4433,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4456,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4501,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,39 +4645,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>3901200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-234400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2853800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6334800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>444500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1687100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1977600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>316600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,39 +4693,42 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>9900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-78900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-104500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-25800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4492,39 +4741,42 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>2181100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>693100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3175200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5752400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-320900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-626100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1065700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4789,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>NIO</t>
   </si>
@@ -662,8 +662,7 @@
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.140625" style="1"/>
@@ -896,7 +895,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1786200</v>
+        <v>1751800</v>
       </c>
       <c r="E12" s="3">
         <v>1855600</v>
@@ -992,13 +991,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>48200</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
-        <v>18800</v>
+        <v>-24000</v>
       </c>
       <c r="F14" s="3">
-        <v>20400</v>
+        <v>-20100</v>
       </c>
       <c r="G14" s="3">
         <v>1036800</v>
@@ -1040,7 +1039,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>462800</v>
+        <v>805000</v>
       </c>
       <c r="E15" s="3">
         <v>476400</v>
@@ -1269,7 +1268,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2616400</v>
+        <v>-2274200</v>
       </c>
       <c r="E21" s="3">
         <v>-2687600</v>
@@ -1365,13 +1364,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3119800</v>
+        <v>-3072200</v>
       </c>
       <c r="E23" s="3">
-        <v>-2928000</v>
+        <v>-2885200</v>
       </c>
       <c r="F23" s="3">
-        <v>-2125700</v>
+        <v>-2085200</v>
       </c>
       <c r="G23" s="3">
         <v>-1662500</v>
@@ -1509,13 +1508,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3116700</v>
+        <v>-3069100</v>
       </c>
       <c r="E26" s="3">
-        <v>-2964800</v>
+        <v>-2922000</v>
       </c>
       <c r="F26" s="3">
-        <v>-2133700</v>
+        <v>-2093200</v>
       </c>
       <c r="G26" s="3">
         <v>-1669200</v>
@@ -2130,7 +2129,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1936900</v>
+        <v>1988400</v>
       </c>
       <c r="E42" s="3">
         <v>2404600</v>
@@ -2178,7 +2177,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1284900</v>
+        <v>1308900</v>
       </c>
       <c r="E43" s="3">
         <v>948800</v>
@@ -2274,7 +2273,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>497700</v>
+        <v>422200</v>
       </c>
       <c r="E45" s="3">
         <v>401400</v>
@@ -2418,7 +2417,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5300700</v>
+        <v>5309400</v>
       </c>
       <c r="E48" s="3">
         <v>5120200</v>
@@ -2610,10 +2609,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>502900</v>
+        <v>375900</v>
       </c>
       <c r="E52" s="3">
-        <v>342100</v>
+        <v>350500</v>
       </c>
       <c r="F52" s="3">
         <v>397300</v>
@@ -2794,10 +2793,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4711200</v>
+        <v>4727100</v>
       </c>
       <c r="E57" s="3">
-        <v>4264800</v>
+        <v>4261200</v>
       </c>
       <c r="F57" s="3">
         <v>3700500</v>
@@ -2842,7 +2841,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1517100</v>
+        <v>1518900</v>
       </c>
       <c r="E58" s="3">
         <v>1634500</v>
@@ -2890,10 +2889,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>110900</v>
+        <v>1363600</v>
       </c>
       <c r="E59" s="3">
-        <v>1270600</v>
+        <v>1334800</v>
       </c>
       <c r="F59" s="3">
         <v>1141100</v>
@@ -2986,7 +2985,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3110200</v>
+        <v>3115000</v>
       </c>
       <c r="E61" s="3">
         <v>3262600</v>
@@ -3034,7 +3033,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1227300</v>
+        <v>751600</v>
       </c>
       <c r="E62" s="3">
         <v>460700</v>
@@ -3485,8 +3484,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-15490700</v>
       </c>
       <c r="E72" s="3">
         <v>-12799200</v>
@@ -3894,8 +3893,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1054300</v>
       </c>
       <c r="E83" s="3">
         <v>691300</v>
@@ -4182,8 +4181,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-1075400</v>
       </c>
       <c r="E89" s="3">
         <v>-194800</v>
@@ -4250,8 +4249,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-1252500</v>
       </c>
       <c r="E91" s="3">
         <v>-2022400</v>
@@ -4394,8 +4393,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-679300</v>
       </c>
       <c r="E94" s="3">
         <v>-1535100</v>
@@ -4654,8 +4653,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>242800</v>
       </c>
       <c r="E100" s="3">
         <v>3901200</v>
@@ -4702,8 +4701,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>22100</v>
       </c>
       <c r="E101" s="3">
         <v>9900</v>
@@ -4751,7 +4750,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-1489800</v>
       </c>
       <c r="E102" s="3">
         <v>2181100</v>

--- a/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NIO_YR_FIN.xlsx
@@ -656,62 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -724,36 +724,39 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12508200</v>
+      </c>
+      <c r="E8" s="3">
         <v>9005400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7843600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7143300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5688400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2490300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1123800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>719900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -769,39 +772,42 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10804600</v>
+      </c>
+      <c r="E9" s="3">
         <v>8115900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7413200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6397500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4614600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2203300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1296000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>757100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,36 +826,39 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1703600</v>
+      </c>
+      <c r="E10" s="3">
         <v>889500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>430400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>745800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1073800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>287000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-172200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-37200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,9 +877,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,41 +901,42 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1482500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1751800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1855600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1543100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>714400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>373200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>627800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>576500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>398100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>201300</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,41 +1000,44 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>600</v>
+        <v>89300</v>
       </c>
       <c r="E14" s="3">
-        <v>-24000</v>
+        <v>48200</v>
       </c>
       <c r="F14" s="3">
-        <v>-20100</v>
+        <v>18800</v>
       </c>
       <c r="G14" s="3">
+        <v>20400</v>
+      </c>
+      <c r="H14" s="3">
         <v>1036800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>47700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1996400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>396000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1032,42 +1051,45 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1021800</v>
+      </c>
+      <c r="E15" s="3">
         <v>805000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>476400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>413500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>268900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>160300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>143500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>69000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6400</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,41 +1123,42 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14515700</v>
+      </c>
+      <c r="E17" s="3">
         <v>12002300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11038500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9411000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6396200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3196000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2715000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2115100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>761300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>359400</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,39 +1171,42 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2007500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2996800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3195000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2267700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-707800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-705800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1591200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1395200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-761300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1193,9 +1222,12 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,38 +1246,39 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E20" s="3">
         <v>82400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-38900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>66000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,39 +1294,42 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1077400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2274200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2687600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1840400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-400000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-611500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1447500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1330700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-745400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,41 +1345,44 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E22" s="3">
         <v>109400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>48300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>65300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>53200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2800</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1357,42 +1396,45 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3072200</v>
+        <v>-2206100</v>
       </c>
       <c r="E23" s="3">
-        <v>-2885200</v>
+        <v>-3119800</v>
       </c>
       <c r="F23" s="3">
-        <v>-2085200</v>
+        <v>-2928000</v>
       </c>
       <c r="G23" s="3">
+        <v>-2125700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1662500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-859200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1639300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3394700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1166500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-354700</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,42 +1447,45 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1453,9 +1498,12 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,42 +1549,45 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3069100</v>
+        <v>-2223600</v>
       </c>
       <c r="E26" s="3">
-        <v>-2922000</v>
+        <v>-3116700</v>
       </c>
       <c r="F26" s="3">
-        <v>-2093200</v>
+        <v>-2964800</v>
       </c>
       <c r="G26" s="3">
+        <v>-2133700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1669200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-860200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1640400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3397900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1167700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-355300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1549,42 +1600,45 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2226200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3104200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2982300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2110900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1664300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-859400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1639100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3391800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1162100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-485700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1597,9 +1651,12 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,39 +1855,42 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-91700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-82400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>38900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-66000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,42 +1906,45 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2226200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3104200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2982300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2110900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1664200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-859400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1639100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3391800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1162100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-485700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1885,9 +1957,12 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,42 +2008,45 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2226200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3104200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2982300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2110900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1664200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-859400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1639100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3391800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1162100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-485700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,47 +2059,50 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2034,9 +2115,12 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,41 +2160,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1611900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2648100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4644700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2883400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2413800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5885700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>123900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>455700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1153600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,39 +2208,42 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2867300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1988400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2404600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2830200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5846700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>612200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>752900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1900</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,45 +2256,48 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1308900</v>
+        <v>2498100</v>
       </c>
       <c r="E43" s="3">
+        <v>1284900</v>
+      </c>
+      <c r="F43" s="3">
         <v>948800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1025700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>756100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>251500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>228100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>142600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,41 +2310,44 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1219700</v>
+      </c>
+      <c r="E44" s="3">
         <v>971000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>744300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1187600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>323700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>165700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>127800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>213000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13700</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
@@ -2266,42 +2361,45 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>422200</v>
+        <v>651200</v>
       </c>
       <c r="E45" s="3">
+        <v>446200</v>
+      </c>
+      <c r="F45" s="3">
         <v>401400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>191500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>206500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>150600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>189700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>197000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>102000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2314,42 +2412,45 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10956300</v>
+      </c>
+      <c r="E46" s="3">
         <v>8478600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9925400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8575900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10018200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7077600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>707800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1769400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1277100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>120800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,41 +2463,44 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>354600</v>
+      </c>
+      <c r="E47" s="3">
         <v>428300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>773800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>921600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>481600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>21600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7200</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3">
+        <v>0</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
@@ -2410,42 +2514,45 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6181500</v>
+      </c>
+      <c r="E48" s="3">
         <v>5309400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5120200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3346600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1645600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>986800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1103800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>705600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>293700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>115000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2458,42 +2565,45 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E49" s="3">
         <v>31700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>30800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>31300</v>
       </c>
       <c r="H49" s="3">
         <v>31300</v>
       </c>
       <c r="I49" s="3">
+        <v>31300</v>
+      </c>
+      <c r="J49" s="3">
         <v>30200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>31600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,9 +2616,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,42 +2718,45 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E52" s="3">
         <v>375900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>350500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>397300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>465700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>130300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>141400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>127900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2650,9 +2769,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,42 +2820,45 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17785800</v>
+      </c>
+      <c r="E54" s="3">
         <v>14742200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16554100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13957000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13047200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8369600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2094200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2739700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1608800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>244500</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,9 +2871,12 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,41 +2916,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7626000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4727100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4261200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2070900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1027200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>477600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>447900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,42 +2964,45 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1111600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1518900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1634500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>918300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1270400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>384600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>266700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2882,42 +3015,45 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1608300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1363600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1334800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1141100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>738200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>440100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>344800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>264300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>90700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,42 +3066,45 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11235100</v>
+      </c>
+      <c r="E60" s="3">
         <v>8536800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8151000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6647900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4596300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2140800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1364200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1249500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>248700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>100300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,42 +3117,45 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3358200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3115000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3262600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2525300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1902800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1073500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1269900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>169800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>98700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3026,42 +3168,45 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>833200</v>
+      </c>
+      <c r="E62" s="3">
         <v>751600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>460700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>367100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>274600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>121100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>61200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>56000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,9 +3219,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,42 +3372,45 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15971100</v>
+      </c>
+      <c r="E66" s="3">
         <v>12891700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12380300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9948600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7055400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3489200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2786700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1554600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>369200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>112400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,9 +3423,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3410,14 +3577,14 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>3021200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>671300</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,42 +3648,45 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18304500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15490700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12799200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10136600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-8757700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7911100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6653300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5094700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1800000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-562900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3526,9 +3699,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,42 +3852,45 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>594700</v>
+      </c>
+      <c r="E76" s="3">
         <v>817500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3602700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3460600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5463900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4161500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-904800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>994100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1783300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-539200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,9 +3903,12 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,47 +3954,50 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3819,42 +4010,45 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2226200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3104200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2982300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2110900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1664200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-859400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1639100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3391800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1162100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-485700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,9 +4061,12 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,41 +4085,42 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1339600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1054300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>691300</v>
       </c>
-      <c r="F83" s="3">
-        <v>578300</v>
-      </c>
       <c r="G83" s="3">
+        <v>579100</v>
+      </c>
+      <c r="H83" s="3">
         <v>369500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>235900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>217600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>68300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3935,9 +4133,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,42 +4388,45 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>427900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1075400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-194800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-560500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>309500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>298800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1252600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1150400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-703100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-304000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,9 +4439,12 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,41 +4463,42 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-867200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1252500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2022400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1011000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-642100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-172700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-245100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-384400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-171200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-90400</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4291,9 +4511,12 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,42 +4613,45 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1638400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-679300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1535100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1505700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6259600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-776700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>485700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1154600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-182900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>16300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4435,9 +4664,12 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,42 +4889,45 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>978500</v>
+      </c>
+      <c r="E100" s="3">
         <v>242800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3901200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-234400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2853800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6334800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>444500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1687100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1977600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>316600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4695,42 +4940,45 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E101" s="3">
         <v>22100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-17700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-78900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-104500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-25800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4743,42 +4991,45 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-234300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1489800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2181100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>693100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3175200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5752400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-320900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-626100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1065700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>34500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,7 +5042,10 @@
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
